--- a/data/raw/data_access.xlsx
+++ b/data/raw/data_access.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zxu567\Documents\R\sia.project.1.wi.data\data\raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\msa583\Downloads\Relational Database_26-02-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="231" documentId="13_ncr:1_{15959687-070F-45CB-84E4-6D2C35395F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15625D07-3687-4834-82E3-9DBA491DC0E5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4484C9E1-62F9-40C9-8CD2-6210A6186303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7A7D6C86-A6AC-403C-91E2-C0E7310CD44B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A7D6C86-A6AC-403C-91E2-C0E7310CD44B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2530" uniqueCount="298">
   <si>
     <t>device_id</t>
   </si>
@@ -382,13 +382,562 @@
   </si>
   <si>
     <t>015_sia_wd_app</t>
+  </si>
+  <si>
+    <t>016_sia_wd_app</t>
+  </si>
+  <si>
+    <t>Bluetooth 5.3 and WiFi</t>
+  </si>
+  <si>
+    <t>iPhone 8 or later with iOS 16 or later</t>
+  </si>
+  <si>
+    <t>017_sia_wd_bio</t>
+  </si>
+  <si>
+    <t>EDRindex, EDRamp, EDL, ΔEDL, HR, HRV, RSA</t>
+  </si>
+  <si>
+    <t>1min: EDRindex, EDRamp, EDL, ΔEDL, HR, HRV, RSA</t>
+  </si>
+  <si>
+    <t>Bluetooth Low-Energy</t>
+  </si>
+  <si>
+    <t>iOS 15.2 or higher</t>
+  </si>
+  <si>
+    <t>Senstream App</t>
+  </si>
+  <si>
+    <t>AcqKnowledge Ring software from Biopac</t>
+  </si>
+  <si>
+    <t>stream and store data via the app - either locally on iPhone or sent to Senstream cloud; via AcqKnowledge - on your PC</t>
+  </si>
+  <si>
+    <t>018_sia_wd_now</t>
+  </si>
+  <si>
+    <t>HR; IBI; RR; activity count; activity type; cadence; sleep stages; steps</t>
+  </si>
+  <si>
+    <t>Bluetooth</t>
+  </si>
+  <si>
+    <t>Android 10 or newer</t>
+  </si>
+  <si>
+    <t>iOS 15.0 or higher</t>
+  </si>
+  <si>
+    <t>NOWATCH app</t>
+  </si>
+  <si>
+    <t>Europe</t>
+  </si>
+  <si>
+    <t>019_sia_wd_goo</t>
+  </si>
+  <si>
+    <t>HR; HRV; Breathing rate; Resting HR; Afib notifications; Daily Readiness score; Active Zone Minutes; Cardio Fitness Score; Exercise tracking; Stress Management score; Sleep score; Sleep time; Sleep stage detection</t>
+  </si>
+  <si>
+    <t>1min: Blood oxygen saturation during sleep; 1hour: HR, Hourly activity, Stress management score, Resting HR; 1day: Sleep time, Sleep stage detection, RR during sleep, HRV, Skin temp, Steps</t>
+  </si>
+  <si>
+    <t>Bluetooth 5.0</t>
+  </si>
+  <si>
+    <t>Android 8.0 or newer</t>
+  </si>
+  <si>
+    <t>Google Pixel Watch app, Fitbit app</t>
+  </si>
+  <si>
+    <t>Fitbit ECG app</t>
+  </si>
+  <si>
+    <t>several countries within the European Economic Area, United Kindom and Switzerland, controlled by Fitbit International Limited, an Irish company.</t>
+  </si>
+  <si>
+    <t>020_sia_wd_goo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HR; HRV; Breathing rate; Resting HR; Afib notifications; Daily Readiness score; Active Zone Minutes; Cardio Fitness Score; Exercise tracking; Stress Management score; Sleep score; Sleep time; Skin temp; SpO2; EDA;  </t>
+  </si>
+  <si>
+    <t>1min: Blood oxygen saturation during sleep; 1hour: Steps; HR (every 2 hours), Hourly activity, Stress management score, Resting HR; 1day: Sleep time, Sleep stage detection, RR during sleep, HRV, Skin temp, Daily blood oxygen saturation, Mean resting HR</t>
+  </si>
+  <si>
+    <t>Bluetooth 5.1</t>
+  </si>
+  <si>
+    <t>Android 9.0 or newer</t>
+  </si>
+  <si>
+    <t>Fitbit ECG app, Fitbit EDA Scan app</t>
+  </si>
+  <si>
+    <t>021_sia_wd_cor</t>
+  </si>
+  <si>
+    <t>Activity; DBP; SBP; Core body temp; EDA; activity ECG; HRV; NIBP; HR; RR; Core body temp; Skin temp; Sleep; Spirometry; SpO2; Steps</t>
+  </si>
+  <si>
+    <t>Bluetooth BLE 5.0</t>
+  </si>
+  <si>
+    <t>Corsano Trials App, Medical cloud storage</t>
+  </si>
+  <si>
+    <t>Corsano Research Portal</t>
+  </si>
+  <si>
+    <t>Corsano medical cloud storage in Switzerland or Germany</t>
+  </si>
+  <si>
+    <t>clearance 510(k)</t>
+  </si>
+  <si>
+    <t>022_sia_wd_cor</t>
+  </si>
+  <si>
+    <t>Activity; HR; HRV; RR; IBI; Afib; steps; cadence; speed; energy expenditure; calorid data; exercise type; sleep classifications</t>
+  </si>
+  <si>
+    <t>Bluetooth BLE</t>
+  </si>
+  <si>
+    <t>023_sia_wd_bio</t>
+  </si>
+  <si>
+    <t>%BF; Body Fat Mass; Skeletal Muscle Mass; HR; Steps; EE; Sleep Amount;Sleep Score;Sleep Stages;Active Time;Distance;Activity Detection</t>
+  </si>
+  <si>
+    <t>1hour: Steps, EE, HR; 1day: Weight, %BF, Body Fat Mass, Skeletal Muscle Mass, Sleep amount, Duration of each sleep stage</t>
+  </si>
+  <si>
+    <t>10.0 or higher</t>
+  </si>
+  <si>
+    <t>15.0 or higher</t>
+  </si>
+  <si>
+    <t>InBody Wear App</t>
+  </si>
+  <si>
+    <t>024_sia_wd_fit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HR; HRV; ns.SCR-MIR; Skin temp; Night SpO2; Night RR; Resting HR; Afib notifications; Daily Readiness score; Active Zone Minutes; Cardio Fitness Score; Steps; Distance; Calories; Exercise tracking; Wellness report; Stress Management score; Sleep log; Sleep Stages; Sleep Score </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1min: HR; 1hour: Distance, Calories, Hourly Activity, Exercise Count, Steps, Stress score, Skin temp; 1day: Night RR, HRV during night </t>
+  </si>
+  <si>
+    <t>Bluetooth 5.0; NFC</t>
+  </si>
+  <si>
+    <t>Android 10.0 or higher</t>
+  </si>
+  <si>
+    <t>Fitbit App</t>
+  </si>
+  <si>
+    <t>025_sia_wd_fit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HR; HRV; EDA (both scan-based and continuous); Skin temp; SpO2; Breathing rate; Resting HR; Afib notifications; Daily Readiness score; Active Zone Minutes; Cardio Fitness Score; Steps; Distance; Calories; Exercise tracking; Wellness report; Stress Management score; Sleep Score; Sleep Score Cumulative; </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1min: HR; 1hour: ns.SCR, Distance, Calories, Hourly Activity, Exercise Count, Steps, Stress score, Skin temp; 1day: Night RR, HRV during night </t>
+  </si>
+  <si>
+    <t>026_sia_wd_gar</t>
+  </si>
+  <si>
+    <t>HR; HR zones; SpO2; VO2max; Active Time; Sleep duration; Steps; Stress score; Recovery time; Body Battery; Speed; Pace; Cadence; RR; Sleep stage detection (no rem)</t>
+  </si>
+  <si>
+    <t>1min: HR; 5mins: Stress score (around 5 to 30mins per score, difficult to say as app shows data over 15 hours in a small graph) 1hour: Body battery, RR (day and night); 1day: Steps, Intensity minutes, Steps, Calories, Average resting HR, Sleep duration, Sleep stage duration (deep,light, awake, no rem); Notes: if an exercise session is manually started, the activity (including pace and cadence) is recorded per minute</t>
+  </si>
+  <si>
+    <t>Bluetooth, ANT+, Wi-Fi</t>
+  </si>
+  <si>
+    <t>Android 7 or higher</t>
+  </si>
+  <si>
+    <t>Garmin Connect</t>
+  </si>
+  <si>
+    <t>Garmin Connect IQ Store; Garmin Dive; Garmin Golf; Garmin Jr.; Garmin ECG</t>
+  </si>
+  <si>
+    <t>several countries, personal data regarding individuals who reside in a country in the European Economic Area, United Kindom or Switzerland is controlled by Garmin Würzburg GmbH; Data from customers in mainland China, is store in GarminChina Shanghai RHQ Co., Ltd's servers in mainland China; Others data will be stored on servers in United States of America, United Kingdom and/or Australia.</t>
+  </si>
+  <si>
+    <t>510(k) clearance for the ECG App</t>
+  </si>
+  <si>
+    <t>027_sia_wd_gar</t>
+  </si>
+  <si>
+    <t>HR; Resting HR; HR zones; HRV; SpO2; VO2max; Active Time; Sleep duration; Stress score; Recovery time; Body Battery; Stress; Speed; Pace; Cadence; RR; Sleep recommendations; RR; Sleep stage detection</t>
+  </si>
+  <si>
+    <t>1min: HR; 5mins: Stress score (around 5 to 30mins per score, difficult to say as app shows data over 15 hours in a small graph) 1hour: Body battery, RR (day and night), Distance; 1day: HRV (nighttime), Steps, Intensity minutes, Steps, Calories, Average resting HR, Sleep duration, Sleep stage duration (deep,light, awake, rem); Notes: if an exercise session is manually started, the activity (including speed and distance) is recorded per minute</t>
+  </si>
+  <si>
+    <t>built-in storage; data has to be transmitted to the coupled Garmin app. Data can be transmitted to your local computer storage</t>
+  </si>
+  <si>
+    <t>028_sia_wd_who</t>
+  </si>
+  <si>
+    <t>HR; Resting (sleep) HR; Blood oxygen saturation; Daily HRV-RMSSD during sleep; Monthly HRV-RMSSD during sleep; Daily RR during sleep; Averaged Monthly RR during sleep; Number of activities; Percentage daily strain; Activity type classification; Calories; Daily % Recovery; Sleep duration; Active time; Monthly maximal HR; Monthly averaged HR; Monthly Calories; Monthly averaged Sleep duration; Daily Bed Time; Averaged Monthly Bed Time; Daily Total Sleep Disturbances; Averaged Monthly Sleep Disturbances; Nightly Needed Sleep; Sleep Stages; Daily Skin Temperature; Stress score; Sleep performance</t>
+  </si>
+  <si>
+    <t>1min: HR; 1hour: Stress score; 1day: Resting (sleep) HR, Blood oxygen saturation, Daily HRV-RMSSD during sleep, Daily RR during sleep, Number of activities, Percentage daily strain, Activity type classification, Calories, Daily % Recovery, Sleep duration, Active time, Daily Bed Time, Daily Total Sleep Disturbances, Nightly Needed Sleep, Sleep Stages, Daily Skin Temperature</t>
+  </si>
+  <si>
+    <t>Bluetooth 4.2 or higher; WiFi</t>
+  </si>
+  <si>
+    <t>iOS 14 or higher, Android OS 10.0 or higher</t>
+  </si>
+  <si>
+    <t>WHOOP App</t>
+  </si>
+  <si>
+    <t>built-in storage; the data should be synced to the app in mobile phone via Bluetooth</t>
+  </si>
+  <si>
+    <t>for the European Economic Area, Switzerland, and UK, the data is stored in accordance with GDPR, exact server locations are not provided, the website notes for Taiwan residents, personal data may be stored in and transferred between any of the servers in the United States, Germany, Japan, United Kingdom, France, Canada, and India</t>
+  </si>
+  <si>
+    <t>029_sia_wd_who</t>
+  </si>
+  <si>
+    <t>030_sia_wd_cir</t>
+  </si>
+  <si>
+    <t>HR; Morning Resting HR; RR during Sleep; Skin Temp; Stress Score; Energy Level; HRV-RMSSD during Sleep; Intermittent HRV-RMSSD; Steps; Sleep Duration; Sleep Disturbances; Sleep efficiency; Tranquility; Circadian Rhythm; REM sleep;  Deep sleep; Time to fall asleep; Sleep debt; Awake times during sleep; Distance; EE;%maxHR; SpO2; Duration of sleep stages</t>
+  </si>
+  <si>
+    <t>1min: HR, HRV, %maxHR, Activity intensity, Sp02; RR; 1hour: Energy level, Stress score; 1day: Sleep Score, Duration of sleep stages, Steps, Calories, Active minutes, EE</t>
+  </si>
+  <si>
+    <t>Bluetooth Smart</t>
+  </si>
+  <si>
+    <t>Android 6.0 or later</t>
+  </si>
+  <si>
+    <t>iOS 11.0 or later</t>
+  </si>
+  <si>
+    <t>Circular</t>
+  </si>
+  <si>
+    <t>built-in storage; data has to be synced with the Circular App in smartphone at least every 10 days as the device cannot store for longer than 10 days</t>
+  </si>
+  <si>
+    <t>031_sia_wd_mov</t>
+  </si>
+  <si>
+    <t>HR; Step Count; RMSSD;EE;HRV;Movement Acceleration;Activity Class;Body Position; Skin Temp; Atmospheric Air Pressure; Angular Rate</t>
+  </si>
+  <si>
+    <t>USB cable; Bluetooth Smart 4.0</t>
+  </si>
+  <si>
+    <t>Windows 7, 8, 8.1, 10</t>
+  </si>
+  <si>
+    <t>SensorManager</t>
+  </si>
+  <si>
+    <t>DataAnalyzer</t>
+  </si>
+  <si>
+    <t>built-in storage; the data is transferred from the local device storage to a PC using a USB cable</t>
+  </si>
+  <si>
+    <t>mn</t>
+  </si>
+  <si>
+    <t>032_sia_wd_wit</t>
+  </si>
+  <si>
+    <t>Afib-MIR; HR; QRS; HR; QT; QTc; SpO2; activity tracking; sleep quality score; sleep stage light; sleep stage deep; sleep duration; sleep interruptions; sleep regularity; menstrual cycle tracking; Breathing disturbances; steps</t>
+  </si>
+  <si>
+    <t>5min: HR;  1day: Sleep Quality Score, Sleep Stage Duration, Sleep SpO2; Daily SpO2, Breathing Disturbances, Activity tracking, Steps</t>
+  </si>
+  <si>
+    <t>Android 10.0 and higher</t>
+  </si>
+  <si>
+    <t>iOS 14 and higher</t>
+  </si>
+  <si>
+    <t>Health Mate app</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>033_sia_wd_wit</t>
+  </si>
+  <si>
+    <t>Afib-MIR; HR; Nighttime HRV; QRS; HR; QT; QTc; SpO2; activity tracking; sleep quality score; sleep stage light; sleep stage deep; sleep duration; sleep interruptions; sleep regularity; Skin temp; menstrual cycle tracking; Breathing disturbances; steps; RR</t>
+  </si>
+  <si>
+    <t>5min: HR; 1day: Sleep Quality Score, Sleep Stage Duration, Sleep SpO2; Daily SpO2, Breathing Disturbances, Activity tracking, Steps, Nighttime HRV</t>
+  </si>
+  <si>
+    <t>Android OS 9 and higher</t>
+  </si>
+  <si>
+    <t>iOS 15 and higher</t>
+  </si>
+  <si>
+    <t>034_sia_wd_spa</t>
+  </si>
+  <si>
+    <t>DBP;SBP;MAP;PP;HR</t>
+  </si>
+  <si>
+    <t>Cable</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Windows 7 SP1 Professional, Ultimate and Enterprise (64 bit), Windows 10 Professional and Enterprise (64 bit),  Windows Server 2012 R2, Windows Server 2016 &amp; 2019</t>
+  </si>
+  <si>
+    <t>Sentinel</t>
+  </si>
+  <si>
+    <t>035_sia_wd_gar</t>
+  </si>
+  <si>
+    <t>RR; Sleep score; Blood oxygen during the day; Blood oxygen during sleep; HR;Daily resting pulse rate; Fitness age; Body battery level; Daily stress score;Steps;EE;Distance;Intensity minutes;HR zones; HR alerts; % HR max; HR calories; Duration of each sleeping stage; Incident Detection; Sleep stage classification (light, deep, REM, awake)</t>
+  </si>
+  <si>
+    <t>1min: HR, Stress Score, Body Battery;  1hour: RR; 5hours: Blood oxygen saturation; 1day: Sleep score, Daily stress score, Duration of each sleeping stage, Fitness age</t>
+  </si>
+  <si>
+    <t>Bluetooth Smart; ANT+</t>
+  </si>
+  <si>
+    <t>Android 7.0 OS and above</t>
+  </si>
+  <si>
+    <t>Apple iOS 16.0 and above</t>
+  </si>
+  <si>
+    <t>Garmin Connect App</t>
+  </si>
+  <si>
+    <t>Garmin Express</t>
+  </si>
+  <si>
+    <t>data of individuals who reside in the European Economic Area, United Kindom or Switzerland is stored by Garmin Würzburg GmbH; Data from customers in China, is store in GarminChina Shanghai RHQ Co., Ltd's servers in mainland China; Others data is stored on servers in United States of America, United Kingdom and/or Australia.</t>
+  </si>
+  <si>
+    <t>036_sia_wd_gar</t>
+  </si>
+  <si>
+    <t>Sleep score; Blood oxygen during the day; Blood oxygen during sleep; HR;Daily resting pulse rate; Fitness age; Body battery level; Daily stress score;Steps;EE;Distance;Intensity minutes;HR zones; HR alerts; % HR max; HR calories; Duration of each sleeping stage; Incident Detection; VO2max; Sleep stage classification (light, deep, REM, awake)</t>
+  </si>
+  <si>
+    <t>1min: HR, Body battery, Stress Score; 5min: SpO2%; 1day: Sleep score, Daily stress score, Duration of each sleeping stage, Fitness age</t>
+  </si>
+  <si>
+    <t>037_sia_wd_gar</t>
+  </si>
+  <si>
+    <t>DPB;SBP;HR</t>
+  </si>
+  <si>
+    <t>Wi-Fi; Bluetooth</t>
+  </si>
+  <si>
+    <t>100 measurements</t>
+  </si>
+  <si>
+    <t>measurements</t>
+  </si>
+  <si>
+    <t>Class II Medical Device; medical assessment of blood pressure and pulse rate</t>
+  </si>
+  <si>
+    <t>038_sia_wd_sky</t>
+  </si>
+  <si>
+    <t>HR; HRV; DBP; SBP; BPV</t>
+  </si>
+  <si>
+    <t>5min: HR, DBP, SBP, BPV</t>
+  </si>
+  <si>
+    <t>Android 6.0 and later</t>
+  </si>
+  <si>
+    <t>iOS 10.0 and later</t>
+  </si>
+  <si>
+    <t>CART BP pro</t>
+  </si>
+  <si>
+    <t>not provided</t>
+  </si>
+  <si>
+    <t>039_sia_wd_ama</t>
+  </si>
+  <si>
+    <t>Readiness score; HR; Blood oxygen saturation; Stress level; Sleep stages; Sleep breathing quality; Daytime naps; Sleep score; HR recovery; EDA; HRV; Emotional response detection; Active minutes; Steps; EE; Physical recovery; Mental recovery; Breathing  quality; VO2max; Training load; Nocturnal resting HR</t>
+  </si>
+  <si>
+    <t>1min: Speed, Cadence;5min: HR, Altitude;1day: Sleep score, Nocturnal resting HR, Breathing quality, Skin temp, Sleep stage durations (light, deep, REM), Count of awake times during sleep, Daily HR, VO2max, Training load</t>
+  </si>
+  <si>
+    <t>BLE</t>
+  </si>
+  <si>
+    <t>Android 7.0 and above</t>
+  </si>
+  <si>
+    <t>iOS 14.0 and above </t>
+  </si>
+  <si>
+    <t>Zepp App</t>
+  </si>
+  <si>
+    <t>the server country is not specified, but the company is based in China</t>
+  </si>
+  <si>
+    <t>040_sia_wd_bio</t>
+  </si>
+  <si>
+    <t>HR; HRV; RR; SpO2; sleep analysis; steps; activity metrics; arterial and peripheral elasticity</t>
+  </si>
+  <si>
+    <t>5min: HR, HRV, SpO2; sleep analysis; steps; activity metrics</t>
+  </si>
+  <si>
+    <t>Vital Science application</t>
+  </si>
+  <si>
+    <t>Remote physiological monitoring  web dashboard</t>
+  </si>
+  <si>
+    <t>041_sia_wd_car</t>
+  </si>
+  <si>
+    <t>Steps; Distance; EE; Core Body temp; HRV-MRR; HRV-SDNN; HRV-RMSSD; HRV-PNN50;HRV-MO; HRV-AMO; HRV-SI; IBI; HR; SpO2; Sleep stage classification (light, deep, awake, REM); RR; Performance; Sleep Tranquility score; Sleep Consistency Score; Sleeptime; Resting HR; Readiness score; EDA; Stress</t>
+  </si>
+  <si>
+    <t>1mins: HR and HRV indices IF Preventicus heartbeats software is used; 5mins: Readiness score; 10mins: HR; 1hour: EE (calories), steps; 1day: Core body temperature, HRV, RR</t>
+  </si>
+  <si>
+    <t>Android 8.0 or higher</t>
+  </si>
+  <si>
+    <t>iOS 12.1 or higher</t>
+  </si>
+  <si>
+    <t>CardioMood Trends</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Preventicus heartbeats</t>
+  </si>
+  <si>
+    <t>Preventicus heartbeats</t>
+  </si>
+  <si>
+    <t>042_sia_wd_sam</t>
+  </si>
+  <si>
+    <t>HR;SpO2;Sleep duration;Energy score; Workout tracking; Skin Temp; Active sleep score; Snoring analysis; Movement during sleep; Sleep latency; RR; Sleep quality score; Sleep routine score; Min HR; Max HR; Period onset estimation using skin temp</t>
+  </si>
+  <si>
+    <t>1hour: SpO2 during sleep, Skin temp, Min HR, Max HR, Movement during sleep;1day: Sleep duration, Sleep stage durations (light, deep, REM, awake), Daily HR, Restfulness score, Mental recovery score, Sleep Score, Physical recovery</t>
+  </si>
+  <si>
+    <t>BLE 5.4</t>
+  </si>
+  <si>
+    <t>Android 11 or above</t>
+  </si>
+  <si>
+    <t>Samsung Health App</t>
+  </si>
+  <si>
+    <t>servers are located in South Korea, U.S.A., several locations in Europe, among other locations</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> it was just released and the company plans to also sell in Europe soon</t>
+  </si>
+  <si>
+    <t>043_sia_wd_goo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steps; Distance; Floors; EE; Readiness score; HR; Sleep quality; Cardio load; Target cardio load; HRV; Resting HR; Sleep stages (light, deep, awake REM); Sp02%; Skin temp variation; RR; Stress management score; Physical calmness; Activity balance; </t>
+  </si>
+  <si>
+    <t>1min: HR; 1hour: Steps, Distance, EE; 1day: Resting HR, RR, SpO2%, Skin temp variation</t>
+  </si>
+  <si>
+    <t>Bluetooth 5.0; Ultra-wideband; Wi-Fi 802.11</t>
+  </si>
+  <si>
+    <t>Google Pixel Watch; Fitbi App; Fitbit ECG App</t>
+  </si>
+  <si>
+    <t>044_sia_wd_adi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HR; HR confidence index; IBI; RR; RR confidence index; Skin Temp; Physiological Welfare Index state; Fall state </t>
+  </si>
+  <si>
+    <t>15sec: all, 5sec:HR (if configured)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cable; system specific-USB cable; Bleutooth Compliance version 2.1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Equivital™ Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equivital™ Qiosk; eqView Professional (Non-Diagnostic); Equivital™ Black Ghost eqView Mobile; </t>
+  </si>
+  <si>
+    <t>045_sia_wd_med</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACC; RR; HR; HRV; % HR max; % HR at anaerobic threshold; SpO2; posture detection; estimated core temp; impact; activity; caloric burn; activity metrics </t>
+  </si>
+  <si>
+    <t>cable; system specific-USB cable; Bleutooth Compliance version 2.1 + EDR and version 4.0</t>
+  </si>
+  <si>
+    <t>Windows 8 or higher</t>
+  </si>
+  <si>
+    <t>SDK Kit</t>
+  </si>
+  <si>
+    <t>Omnisense software</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -417,6 +966,66 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF040C28"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF323130"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -426,7 +1035,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -452,11 +1061,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -466,24 +1085,55 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{0F736636-9C85-4CE0-BCA5-8C3EAE169E37}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -815,15 +1465,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA1BD5DC-A81B-4D9C-8626-3C643AFB0E7B}">
-  <dimension ref="A1:F290"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:F766"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" customWidth="1"/>
-    <col min="2" max="2" width="20.28515625" customWidth="1"/>
-    <col min="3" max="3" width="21.28515625" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="16.5546875" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" style="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -842,7 +1492,7 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="17" t="s">
         <v>5</v>
       </c>
     </row>
@@ -864,7 +1514,7 @@
       <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
@@ -875,7 +1525,7 @@
       <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="14" t="s">
         <v>10</v>
       </c>
     </row>
@@ -886,7 +1536,7 @@
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="14" t="s">
         <v>13</v>
       </c>
     </row>
@@ -900,7 +1550,7 @@
       <c r="C6" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="14" t="s">
         <v>15</v>
       </c>
     </row>
@@ -914,7 +1564,7 @@
       <c r="C7" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="14" t="s">
         <v>10</v>
       </c>
     </row>
@@ -928,7 +1578,7 @@
       <c r="C8" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="14" t="s">
         <v>18</v>
       </c>
     </row>
@@ -942,7 +1592,7 @@
       <c r="C9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="14" t="s">
         <v>20</v>
       </c>
     </row>
@@ -956,7 +1606,7 @@
       <c r="C10" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -970,7 +1620,7 @@
       <c r="C11" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="14" t="s">
         <v>24</v>
       </c>
     </row>
@@ -984,7 +1634,7 @@
       <c r="C12" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="14" t="s">
         <v>26</v>
       </c>
     </row>
@@ -998,7 +1648,7 @@
       <c r="C13" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="14" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1073,7 +1723,7 @@
       <c r="C19" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F19" s="7"/>
+      <c r="F19" s="18"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
@@ -1082,7 +1732,7 @@
       <c r="B20" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="14" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1093,7 +1743,7 @@
       <c r="B21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="14" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1104,7 +1754,7 @@
       <c r="B22" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="14" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1118,7 +1768,7 @@
       <c r="C23" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="14" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1132,7 +1782,7 @@
       <c r="C24" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="14" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1146,7 +1796,7 @@
       <c r="C25" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="14" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1160,7 +1810,7 @@
       <c r="C26" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="14" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1174,7 +1824,7 @@
       <c r="C27" t="s">
         <v>8</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="14" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1196,7 +1846,7 @@
       <c r="C29" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F29" s="14" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1260,24 +1910,24 @@
       <c r="C34" t="s">
         <v>8</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="F34" s="14" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="35" spans="1:6" s="9" customFormat="1">
-      <c r="A35" s="9" t="s">
+    <row r="35" spans="1:6" s="6" customFormat="1">
+      <c r="A35" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C35" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" s="11"/>
+      <c r="C35" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="19"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B36" s="2" t="s">
@@ -1288,40 +1938,40 @@
       </c>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="F37" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F38" s="6" t="s">
+      <c r="F38" s="14" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" s="14" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B40" s="2" t="s">
@@ -1330,12 +1980,12 @@
       <c r="C40" t="s">
         <v>8</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="F40" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B41" s="2" t="s">
@@ -1344,12 +1994,12 @@
       <c r="C41" t="s">
         <v>8</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="F41" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="42" spans="1:6">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B42" s="2" t="s">
@@ -1360,7 +2010,7 @@
       </c>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B43" s="2" t="s">
@@ -1371,7 +2021,7 @@
       </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B44" s="2" t="s">
@@ -1380,12 +2030,12 @@
       <c r="C44" t="s">
         <v>8</v>
       </c>
-      <c r="F44" s="6" t="s">
+      <c r="F44" s="14" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="45" spans="1:6">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B45" s="2" t="s">
@@ -1396,7 +2046,7 @@
       </c>
     </row>
     <row r="46" spans="1:6">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
@@ -1405,12 +2055,12 @@
       <c r="C46" t="s">
         <v>8</v>
       </c>
-      <c r="F46" s="6" t="s">
+      <c r="F46" s="14" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B47" s="2" t="s">
@@ -1421,21 +2071,21 @@
       </c>
     </row>
     <row r="48" spans="1:6">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D48" s="13" t="s">
-        <v>48</v>
+      <c r="D48">
+        <v>-9999</v>
       </c>
       <c r="E48" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B49" s="2" t="s">
@@ -1449,7 +2099,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B50" s="2" t="s">
@@ -1460,7 +2110,7 @@
       </c>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B51" s="2" t="s">
@@ -1470,17 +2120,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="52" spans="1:6" s="9" customFormat="1">
-      <c r="A52" s="12" t="s">
+    <row r="52" spans="1:6" s="6" customFormat="1">
+      <c r="A52" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="B52" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C52" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" s="11"/>
+      <c r="C52" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="19"/>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
@@ -1500,7 +2150,7 @@
       <c r="B54" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F54" s="6" t="s">
+      <c r="F54" s="14" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1511,7 +2161,7 @@
       <c r="B55" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F55" s="6" t="s">
+      <c r="F55" s="14" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1522,7 +2172,7 @@
       <c r="B56" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F56" s="6" t="s">
+      <c r="F56" s="14" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1536,7 +2186,7 @@
       <c r="C57" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="6" t="s">
+      <c r="F57" s="14" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1550,7 +2200,7 @@
       <c r="C58" t="s">
         <v>8</v>
       </c>
-      <c r="F58" s="6" t="s">
+      <c r="F58" s="14" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1586,7 +2236,7 @@
       <c r="C61" t="s">
         <v>8</v>
       </c>
-      <c r="F61" s="6" t="s">
+      <c r="F61" s="14" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1611,7 +2261,7 @@
       <c r="C63" t="s">
         <v>8</v>
       </c>
-      <c r="F63" s="6" t="s">
+      <c r="F63" s="14" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1676,20 +2326,20 @@
         <v>35</v>
       </c>
     </row>
-    <row r="69" spans="1:6" s="9" customFormat="1">
-      <c r="A69" s="9" t="s">
+    <row r="69" spans="1:6" s="6" customFormat="1">
+      <c r="A69" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B69" s="10" t="s">
+      <c r="B69" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C69" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F69" s="11"/>
+      <c r="C69" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F69" s="19"/>
     </row>
     <row r="70" spans="1:6">
-      <c r="A70" s="8" t="s">
+      <c r="A70" s="5" t="s">
         <v>55</v>
       </c>
       <c r="B70" s="2" t="s">
@@ -1700,40 +2350,40 @@
       </c>
     </row>
     <row r="71" spans="1:6">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="5" t="s">
         <v>55</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F71" s="6" t="s">
+      <c r="F71" s="14" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="8" t="s">
+      <c r="A72" s="5" t="s">
         <v>55</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F72" s="6" t="s">
+      <c r="F72" s="14" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="5" t="s">
         <v>55</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F73" s="6" t="s">
+      <c r="F73" s="14" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="74" spans="1:6">
-      <c r="A74" s="8" t="s">
+      <c r="A74" s="5" t="s">
         <v>55</v>
       </c>
       <c r="B74" s="2" t="s">
@@ -1744,7 +2394,7 @@
       </c>
     </row>
     <row r="75" spans="1:6">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="5" t="s">
         <v>55</v>
       </c>
       <c r="B75" s="2" t="s">
@@ -1755,7 +2405,7 @@
       </c>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="8" t="s">
+      <c r="A76" s="5" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="2" t="s">
@@ -1764,12 +2414,12 @@
       <c r="C76" t="s">
         <v>8</v>
       </c>
-      <c r="F76" s="6" t="s">
+      <c r="F76" s="14" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="A77" s="8" t="s">
+      <c r="A77" s="5" t="s">
         <v>55</v>
       </c>
       <c r="B77" s="2" t="s">
@@ -1778,12 +2428,12 @@
       <c r="C77" t="s">
         <v>8</v>
       </c>
-      <c r="F77" s="6" t="s">
+      <c r="F77" s="14" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="8" t="s">
+      <c r="A78" s="5" t="s">
         <v>55</v>
       </c>
       <c r="B78" s="2" t="s">
@@ -1792,12 +2442,12 @@
       <c r="C78" t="s">
         <v>8</v>
       </c>
-      <c r="F78" s="6" t="s">
+      <c r="F78" s="14" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="79" spans="1:6">
-      <c r="A79" s="8" t="s">
+      <c r="A79" s="5" t="s">
         <v>55</v>
       </c>
       <c r="B79" s="2" t="s">
@@ -1806,12 +2456,12 @@
       <c r="C79" t="s">
         <v>8</v>
       </c>
-      <c r="F79" s="6" t="s">
+      <c r="F79" s="14" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="80" spans="1:6">
-      <c r="A80" s="8" t="s">
+      <c r="A80" s="5" t="s">
         <v>55</v>
       </c>
       <c r="B80" s="2" t="s">
@@ -1820,12 +2470,12 @@
       <c r="C80" t="s">
         <v>8</v>
       </c>
-      <c r="F80" s="6" t="s">
+      <c r="F80" s="14" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="81" spans="1:6">
-      <c r="A81" s="8" t="s">
+      <c r="A81" s="5" t="s">
         <v>55</v>
       </c>
       <c r="B81" s="2" t="s">
@@ -1834,40 +2484,40 @@
       <c r="C81" t="s">
         <v>8</v>
       </c>
-      <c r="F81" s="6" t="s">
+      <c r="F81" s="14" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="82" spans="1:6">
-      <c r="A82" s="8" t="s">
+      <c r="A82" s="5" t="s">
         <v>55</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D82" t="s">
-        <v>48</v>
+      <c r="D82">
+        <v>-9999</v>
       </c>
       <c r="E82" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="83" spans="1:6">
-      <c r="A83" s="8" t="s">
+      <c r="A83" s="5" t="s">
         <v>55</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D83" t="s">
-        <v>48</v>
+      <c r="D83">
+        <v>-9999</v>
       </c>
       <c r="E83" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="84" spans="1:6">
-      <c r="A84" s="8" t="s">
+      <c r="A84" s="5" t="s">
         <v>55</v>
       </c>
       <c r="B84" s="2" t="s">
@@ -1878,7 +2528,7 @@
       </c>
     </row>
     <row r="85" spans="1:6">
-      <c r="A85" s="8" t="s">
+      <c r="A85" s="5" t="s">
         <v>55</v>
       </c>
       <c r="B85" s="2" t="s">
@@ -1887,21 +2537,21 @@
       <c r="C85" t="s">
         <v>8</v>
       </c>
-      <c r="F85" s="6" t="s">
+      <c r="F85" s="14" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="86" spans="1:6" s="9" customFormat="1">
-      <c r="A86" s="12" t="s">
+    <row r="86" spans="1:6" s="6" customFormat="1">
+      <c r="A86" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B86" s="10" t="s">
+      <c r="B86" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C86" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F86" s="11"/>
+      <c r="C86" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F86" s="19"/>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
@@ -1921,7 +2571,7 @@
       <c r="B88" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F88" s="6" t="s">
+      <c r="F88" s="14" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1932,7 +2582,7 @@
       <c r="B89" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F89" s="6" t="s">
+      <c r="F89" s="14" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1943,7 +2593,7 @@
       <c r="B90" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F90" s="6" t="s">
+      <c r="F90" s="14" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1954,7 +2604,7 @@
       <c r="B91" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C91" s="14" t="s">
+      <c r="C91" s="9" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1965,7 +2615,7 @@
       <c r="B92" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C92" s="14" t="s">
+      <c r="C92" s="9" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1976,7 +2626,7 @@
       <c r="B93" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C93" s="14" t="s">
+      <c r="C93" s="9" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1987,7 +2637,7 @@
       <c r="B94" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C94" s="14" t="s">
+      <c r="C94" s="9" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2001,7 +2651,7 @@
       <c r="C95" t="s">
         <v>8</v>
       </c>
-      <c r="F95" s="6" t="s">
+      <c r="F95" s="14" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2026,7 +2676,7 @@
       <c r="C97" t="s">
         <v>8</v>
       </c>
-      <c r="F97" s="6" t="s">
+      <c r="F97" s="14" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2062,8 +2712,8 @@
       <c r="B100" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D100" t="s">
-        <v>48</v>
+      <c r="D100">
+        <v>-9999</v>
       </c>
       <c r="E100" t="s">
         <v>32</v>
@@ -2091,17 +2741,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="103" spans="1:6" s="9" customFormat="1">
-      <c r="A103" s="9" t="s">
+    <row r="103" spans="1:6" s="6" customFormat="1">
+      <c r="A103" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B103" s="10" t="s">
+      <c r="B103" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C103" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F103" s="11"/>
+      <c r="C103" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F103" s="19"/>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
@@ -2121,7 +2771,7 @@
       <c r="B105" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F105" s="6" t="s">
+      <c r="F105" s="14" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2132,7 +2782,7 @@
       <c r="B106" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F106" s="6" t="s">
+      <c r="F106" s="14" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2143,7 +2793,7 @@
       <c r="B107" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F107" s="6" t="s">
+      <c r="F107" s="14" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2154,7 +2804,7 @@
       <c r="B108" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C108" s="14" t="s">
+      <c r="C108" s="9" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2165,7 +2815,7 @@
       <c r="B109" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C109" s="14" t="s">
+      <c r="C109" s="9" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2176,7 +2826,7 @@
       <c r="B110" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C110" s="14" t="s">
+      <c r="C110" s="9" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2187,7 +2837,7 @@
       <c r="B111" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C111" s="14" t="s">
+      <c r="C111" s="9" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2201,7 +2851,7 @@
       <c r="C112" t="s">
         <v>8</v>
       </c>
-      <c r="F112" s="6" t="s">
+      <c r="F112" s="14" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2226,7 +2876,7 @@
       <c r="C114" t="s">
         <v>8</v>
       </c>
-      <c r="F114" s="6" t="s">
+      <c r="F114" s="14" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2262,8 +2912,8 @@
       <c r="B117" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D117" t="s">
-        <v>48</v>
+      <c r="D117">
+        <v>-9999</v>
       </c>
       <c r="E117" t="s">
         <v>32</v>
@@ -2291,17 +2941,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="120" spans="1:6" s="9" customFormat="1">
-      <c r="A120" s="9" t="s">
+    <row r="120" spans="1:6" s="6" customFormat="1">
+      <c r="A120" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B120" s="10" t="s">
+      <c r="B120" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C120" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F120" s="11"/>
+      <c r="C120" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F120" s="19"/>
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
@@ -2321,7 +2971,7 @@
       <c r="B122" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F122" s="6" t="s">
+      <c r="F122" s="14" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2332,7 +2982,7 @@
       <c r="B123" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F123" s="6" t="s">
+      <c r="F123" s="14" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2343,7 +2993,7 @@
       <c r="B124" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F124" s="6" t="s">
+      <c r="F124" s="14" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2354,7 +3004,7 @@
       <c r="B125" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C125" s="14" t="s">
+      <c r="C125" s="9" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2365,7 +3015,7 @@
       <c r="B126" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C126" s="14" t="s">
+      <c r="C126" s="9" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2376,7 +3026,7 @@
       <c r="B127" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C127" s="14" t="s">
+      <c r="C127" s="9" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2387,7 +3037,7 @@
       <c r="B128" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C128" s="14" t="s">
+      <c r="C128" s="9" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2401,7 +3051,7 @@
       <c r="C129" t="s">
         <v>8</v>
       </c>
-      <c r="F129" s="6" t="s">
+      <c r="F129" s="14" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2426,7 +3076,7 @@
       <c r="C131" t="s">
         <v>8</v>
       </c>
-      <c r="F131" s="6" t="s">
+      <c r="F131" s="14" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2462,8 +3112,8 @@
       <c r="B134" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D134" t="s">
-        <v>48</v>
+      <c r="D134">
+        <v>-9999</v>
       </c>
       <c r="E134" t="s">
         <v>32</v>
@@ -2491,17 +3141,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="137" spans="1:6" s="9" customFormat="1">
-      <c r="A137" s="9" t="s">
+    <row r="137" spans="1:6" s="6" customFormat="1">
+      <c r="A137" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B137" s="10" t="s">
+      <c r="B137" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C137" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F137" s="11"/>
+      <c r="C137" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F137" s="19"/>
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
@@ -2521,7 +3171,7 @@
       <c r="B139" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F139" s="6" t="s">
+      <c r="F139" s="14" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2532,7 +3182,7 @@
       <c r="B140" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F140" s="6" t="s">
+      <c r="F140" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -2543,7 +3193,7 @@
       <c r="B141" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F141" s="6" t="s">
+      <c r="F141" s="14" t="s">
         <v>75</v>
       </c>
     </row>
@@ -2579,7 +3229,7 @@
       <c r="C144" t="s">
         <v>8</v>
       </c>
-      <c r="F144" s="6" t="s">
+      <c r="F144" s="14" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2593,7 +3243,7 @@
       <c r="C145" t="s">
         <v>8</v>
       </c>
-      <c r="F145" s="6" t="s">
+      <c r="F145" s="14" t="s">
         <v>76</v>
       </c>
     </row>
@@ -2607,7 +3257,7 @@
       <c r="C146" t="s">
         <v>8</v>
       </c>
-      <c r="F146" s="6" t="s">
+      <c r="F146" s="14" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2632,7 +3282,7 @@
       <c r="C148" t="s">
         <v>8</v>
       </c>
-      <c r="F148" s="6" t="s">
+      <c r="F148" s="14" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2646,7 +3296,7 @@
       <c r="C149" t="s">
         <v>8</v>
       </c>
-      <c r="F149" s="6" t="s">
+      <c r="F149" s="14" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2671,8 +3321,8 @@
       <c r="B151" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D151" t="s">
-        <v>48</v>
+      <c r="D151">
+        <v>-9999</v>
       </c>
       <c r="E151" t="s">
         <v>32</v>
@@ -2700,20 +3350,20 @@
         <v>35</v>
       </c>
     </row>
-    <row r="154" spans="1:6" s="9" customFormat="1">
-      <c r="A154" s="9" t="s">
+    <row r="154" spans="1:6" s="6" customFormat="1">
+      <c r="A154" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B154" s="10" t="s">
+      <c r="B154" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C154" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F154" s="11"/>
+      <c r="C154" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F154" s="19"/>
     </row>
     <row r="155" spans="1:6">
-      <c r="A155" s="8" t="s">
+      <c r="A155" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B155" s="2" t="s">
@@ -2724,84 +3374,84 @@
       </c>
     </row>
     <row r="156" spans="1:6">
-      <c r="A156" s="8" t="s">
+      <c r="A156" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F156" s="6" t="s">
+      <c r="F156" s="14" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="157" spans="1:6">
-      <c r="A157" s="8" t="s">
+      <c r="A157" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F157" s="6" t="s">
+      <c r="F157" s="14" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="158" spans="1:6">
-      <c r="A158" s="8" t="s">
+      <c r="A158" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F158" s="6" t="s">
+      <c r="F158" s="14" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="159" spans="1:6">
-      <c r="A159" s="8" t="s">
+      <c r="A159" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C159" s="14" t="s">
+      <c r="C159" s="9" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="160" spans="1:6">
-      <c r="A160" s="8" t="s">
+      <c r="A160" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C160" s="14" t="s">
+      <c r="C160" s="9" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="161" spans="1:6">
-      <c r="A161" s="8" t="s">
+      <c r="A161" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C161" s="14" t="s">
+      <c r="C161" s="9" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="162" spans="1:6">
-      <c r="A162" s="8" t="s">
+      <c r="A162" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C162" s="14" t="s">
+      <c r="C162" s="9" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="163" spans="1:6">
-      <c r="A163" s="8" t="s">
+      <c r="A163" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B163" s="2" t="s">
@@ -2810,12 +3460,12 @@
       <c r="C163" t="s">
         <v>8</v>
       </c>
-      <c r="F163" s="6" t="s">
+      <c r="F163" s="14" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="164" spans="1:6">
-      <c r="A164" s="8" t="s">
+      <c r="A164" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B164" s="2" t="s">
@@ -2826,7 +3476,7 @@
       </c>
     </row>
     <row r="165" spans="1:6">
-      <c r="A165" s="8" t="s">
+      <c r="A165" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B165" s="2" t="s">
@@ -2835,12 +3485,12 @@
       <c r="C165" t="s">
         <v>8</v>
       </c>
-      <c r="F165" s="6" t="s">
+      <c r="F165" s="14" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="166" spans="1:6">
-      <c r="A166" s="8" t="s">
+      <c r="A166" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B166" s="2" t="s">
@@ -2851,7 +3501,7 @@
       </c>
     </row>
     <row r="167" spans="1:6">
-      <c r="A167" s="8" t="s">
+      <c r="A167" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B167" s="2" t="s">
@@ -2865,7 +3515,7 @@
       </c>
     </row>
     <row r="168" spans="1:6">
-      <c r="A168" s="8" t="s">
+      <c r="A168" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B168" s="2" t="s">
@@ -2879,7 +3529,7 @@
       </c>
     </row>
     <row r="169" spans="1:6">
-      <c r="A169" s="8" t="s">
+      <c r="A169" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B169" s="2" t="s">
@@ -2888,12 +3538,12 @@
       <c r="C169" t="s">
         <v>8</v>
       </c>
-      <c r="F169" s="15" t="s">
+      <c r="F169" s="20" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="170" spans="1:6">
-      <c r="A170" s="8" t="s">
+      <c r="A170" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B170" s="2" t="s">
@@ -2903,20 +3553,20 @@
         <v>35</v>
       </c>
     </row>
-    <row r="171" spans="1:6" s="9" customFormat="1">
-      <c r="A171" s="12" t="s">
+    <row r="171" spans="1:6" s="6" customFormat="1">
+      <c r="A171" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B171" s="10" t="s">
+      <c r="B171" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C171" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F171" s="11"/>
+      <c r="C171" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F171" s="19"/>
     </row>
     <row r="172" spans="1:6">
-      <c r="A172" s="8" t="s">
+      <c r="A172" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B172" s="2" t="s">
@@ -2927,40 +3577,40 @@
       </c>
     </row>
     <row r="173" spans="1:6">
-      <c r="A173" s="8" t="s">
+      <c r="A173" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F173" s="6" t="s">
+      <c r="F173" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="174" spans="1:6">
-      <c r="A174" s="8" t="s">
+      <c r="A174" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F174" s="6" t="s">
+      <c r="F174" s="14" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="175" spans="1:6">
-      <c r="A175" s="8" t="s">
+      <c r="A175" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F175" s="6" t="s">
+      <c r="F175" s="14" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="176" spans="1:6">
-      <c r="A176" s="8" t="s">
+      <c r="A176" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B176" s="2" t="s">
@@ -2971,7 +3621,7 @@
       </c>
     </row>
     <row r="177" spans="1:6">
-      <c r="A177" s="8" t="s">
+      <c r="A177" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B177" s="2" t="s">
@@ -2982,7 +3632,7 @@
       </c>
     </row>
     <row r="178" spans="1:6">
-      <c r="A178" s="8" t="s">
+      <c r="A178" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B178" s="2" t="s">
@@ -2993,7 +3643,7 @@
       </c>
     </row>
     <row r="179" spans="1:6">
-      <c r="A179" s="8" t="s">
+      <c r="A179" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B179" s="2" t="s">
@@ -3004,7 +3654,7 @@
       </c>
     </row>
     <row r="180" spans="1:6">
-      <c r="A180" s="8" t="s">
+      <c r="A180" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B180" s="2" t="s">
@@ -3013,12 +3663,12 @@
       <c r="C180" t="s">
         <v>8</v>
       </c>
-      <c r="F180" s="6" t="s">
+      <c r="F180" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="181" spans="1:6">
-      <c r="A181" s="8" t="s">
+      <c r="A181" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B181" s="2" t="s">
@@ -3027,12 +3677,12 @@
       <c r="C181" t="s">
         <v>8</v>
       </c>
-      <c r="F181" s="6" t="s">
+      <c r="F181" s="14" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="A182" s="8" t="s">
+      <c r="A182" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B182" s="2" t="s">
@@ -3041,12 +3691,12 @@
       <c r="C182" t="s">
         <v>8</v>
       </c>
-      <c r="F182" s="6" t="s">
+      <c r="F182" s="14" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="183" spans="1:6">
-      <c r="A183" s="8" t="s">
+      <c r="A183" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B183" s="2" t="s">
@@ -3057,35 +3707,35 @@
       </c>
     </row>
     <row r="184" spans="1:6">
-      <c r="A184" s="8" t="s">
+      <c r="A184" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D184" t="s">
-        <v>48</v>
+      <c r="D184">
+        <v>-9999</v>
       </c>
       <c r="E184" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="185" spans="1:6">
-      <c r="A185" s="8" t="s">
+      <c r="A185" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D185" t="s">
-        <v>48</v>
+      <c r="D185">
+        <v>-9999</v>
       </c>
       <c r="E185" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="186" spans="1:6">
-      <c r="A186" s="8" t="s">
+      <c r="A186" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B186" s="2" t="s">
@@ -3094,12 +3744,12 @@
       <c r="C186" t="s">
         <v>8</v>
       </c>
-      <c r="F186" s="15" t="s">
+      <c r="F186" s="20" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="187" spans="1:6">
-      <c r="A187" s="8" t="s">
+      <c r="A187" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B187" s="2" t="s">
@@ -3109,17 +3759,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="188" spans="1:6" s="9" customFormat="1">
-      <c r="A188" s="12" t="s">
+    <row r="188" spans="1:6" s="6" customFormat="1">
+      <c r="A188" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="B188" s="10" t="s">
+      <c r="B188" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C188" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F188" s="11"/>
+      <c r="C188" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F188" s="19"/>
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
@@ -3139,7 +3789,7 @@
       <c r="B190" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F190" s="6" t="s">
+      <c r="F190" s="14" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3150,7 +3800,7 @@
       <c r="B191" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F191" s="6" t="s">
+      <c r="F191" s="14" t="s">
         <v>93</v>
       </c>
     </row>
@@ -3161,7 +3811,7 @@
       <c r="B192" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F192" s="6" t="s">
+      <c r="F192" s="14" t="s">
         <v>94</v>
       </c>
     </row>
@@ -3175,7 +3825,7 @@
       <c r="C193" t="s">
         <v>8</v>
       </c>
-      <c r="F193" s="6" t="s">
+      <c r="F193" s="14" t="s">
         <v>95</v>
       </c>
     </row>
@@ -3189,7 +3839,7 @@
       <c r="C194" t="s">
         <v>8</v>
       </c>
-      <c r="F194" s="6" t="s">
+      <c r="F194" s="14" t="s">
         <v>96</v>
       </c>
     </row>
@@ -3203,7 +3853,7 @@
       <c r="C195" t="s">
         <v>8</v>
       </c>
-      <c r="F195" s="6" t="s">
+      <c r="F195" s="14" t="s">
         <v>97</v>
       </c>
     </row>
@@ -3217,7 +3867,7 @@
       <c r="C196" t="s">
         <v>8</v>
       </c>
-      <c r="F196" s="6" t="s">
+      <c r="F196" s="14" t="s">
         <v>98</v>
       </c>
     </row>
@@ -3231,7 +3881,7 @@
       <c r="C197" t="s">
         <v>8</v>
       </c>
-      <c r="F197" s="6" t="s">
+      <c r="F197" s="14" t="s">
         <v>99</v>
       </c>
     </row>
@@ -3245,7 +3895,7 @@
       <c r="C198" t="s">
         <v>8</v>
       </c>
-      <c r="F198" s="6" t="s">
+      <c r="F198" s="14" t="s">
         <v>100</v>
       </c>
     </row>
@@ -3259,7 +3909,7 @@
       <c r="C199" t="s">
         <v>8</v>
       </c>
-      <c r="F199" s="6" t="s">
+      <c r="F199" s="14" t="s">
         <v>26</v>
       </c>
     </row>
@@ -3273,7 +3923,7 @@
       <c r="C200" t="s">
         <v>8</v>
       </c>
-      <c r="F200" s="6" t="s">
+      <c r="F200" s="14" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3298,8 +3948,8 @@
       <c r="B202" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D202" t="s">
-        <v>48</v>
+      <c r="D202">
+        <v>-9999</v>
       </c>
       <c r="E202" t="s">
         <v>32</v>
@@ -3327,17 +3977,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="205" spans="1:6" s="9" customFormat="1">
-      <c r="A205" s="9" t="s">
+    <row r="205" spans="1:6" s="6" customFormat="1">
+      <c r="A205" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B205" s="10" t="s">
+      <c r="B205" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C205" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F205" s="11"/>
+      <c r="C205" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F205" s="19"/>
     </row>
     <row r="206" spans="1:6">
       <c r="A206" t="s">
@@ -3357,7 +4007,7 @@
       <c r="B207" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F207" s="6" t="s">
+      <c r="F207" s="14" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3368,7 +4018,7 @@
       <c r="B208" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F208" s="6" t="s">
+      <c r="F208" s="14" t="s">
         <v>103</v>
       </c>
     </row>
@@ -3379,7 +4029,7 @@
       <c r="B209" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F209" s="6" t="s">
+      <c r="F209" s="14" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3426,7 +4076,7 @@
       <c r="C213" t="s">
         <v>8</v>
       </c>
-      <c r="F213" s="6" t="s">
+      <c r="F213" s="14" t="s">
         <v>105</v>
       </c>
     </row>
@@ -3440,7 +4090,7 @@
       <c r="C214" t="s">
         <v>8</v>
       </c>
-      <c r="F214" s="6" t="s">
+      <c r="F214" s="14" t="s">
         <v>106</v>
       </c>
     </row>
@@ -3465,7 +4115,7 @@
       <c r="C216" t="s">
         <v>8</v>
       </c>
-      <c r="F216" s="6" t="s">
+      <c r="F216" s="14" t="s">
         <v>107</v>
       </c>
     </row>
@@ -3479,7 +4129,7 @@
       <c r="C217" t="s">
         <v>8</v>
       </c>
-      <c r="F217" s="6" t="s">
+      <c r="F217" s="14" t="s">
         <v>108</v>
       </c>
     </row>
@@ -3490,8 +4140,8 @@
       <c r="B218" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D218" t="s">
-        <v>48</v>
+      <c r="D218">
+        <v>-9999</v>
       </c>
       <c r="E218" t="s">
         <v>30</v>
@@ -3532,21 +4182,21 @@
       <c r="C221" t="s">
         <v>8</v>
       </c>
-      <c r="F221" s="6" t="s">
+      <c r="F221" s="14" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="222" spans="1:6" s="9" customFormat="1">
-      <c r="A222" s="9" t="s">
+    <row r="222" spans="1:6" s="6" customFormat="1">
+      <c r="A222" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B222" s="10" t="s">
+      <c r="B222" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C222" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F222" s="11"/>
+      <c r="C222" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F222" s="19"/>
     </row>
     <row r="223" spans="1:6">
       <c r="A223" t="s">
@@ -3566,7 +4216,7 @@
       <c r="B224" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F224" s="6" t="s">
+      <c r="F224" s="14" t="s">
         <v>111</v>
       </c>
     </row>
@@ -3577,7 +4227,7 @@
       <c r="B225" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F225" s="6" t="s">
+      <c r="F225" s="14" t="s">
         <v>103</v>
       </c>
     </row>
@@ -3588,7 +4238,7 @@
       <c r="B226" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F226" s="6" t="s">
+      <c r="F226" s="14" t="s">
         <v>112</v>
       </c>
     </row>
@@ -3635,7 +4285,7 @@
       <c r="C230" t="s">
         <v>8</v>
       </c>
-      <c r="F230" s="6" t="s">
+      <c r="F230" s="14" t="s">
         <v>113</v>
       </c>
     </row>
@@ -3649,7 +4299,7 @@
       <c r="C231" t="s">
         <v>8</v>
       </c>
-      <c r="F231" s="6" t="s">
+      <c r="F231" s="14" t="s">
         <v>106</v>
       </c>
     </row>
@@ -3674,7 +4324,7 @@
       <c r="C233" t="s">
         <v>8</v>
       </c>
-      <c r="F233" s="6" t="s">
+      <c r="F233" s="14" t="s">
         <v>107</v>
       </c>
     </row>
@@ -3688,7 +4338,7 @@
       <c r="C234" t="s">
         <v>8</v>
       </c>
-      <c r="F234" s="6" t="s">
+      <c r="F234" s="14" t="s">
         <v>108</v>
       </c>
     </row>
@@ -3699,8 +4349,8 @@
       <c r="B235" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D235" t="s">
-        <v>48</v>
+      <c r="D235">
+        <v>-9999</v>
       </c>
       <c r="E235" t="s">
         <v>30</v>
@@ -3741,21 +4391,21 @@
       <c r="C238" t="s">
         <v>8</v>
       </c>
-      <c r="F238" s="6" t="s">
+      <c r="F238" s="14" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="239" spans="1:6" s="9" customFormat="1">
-      <c r="A239" s="9" t="s">
+    <row r="239" spans="1:6" s="6" customFormat="1">
+      <c r="A239" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="B239" s="10" t="s">
+      <c r="B239" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C239" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F239" s="11"/>
+      <c r="C239" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F239" s="19"/>
     </row>
     <row r="240" spans="1:6">
       <c r="A240" t="s">
@@ -3775,7 +4425,7 @@
       <c r="B241" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F241" s="6" t="s">
+      <c r="F241" s="14" t="s">
         <v>111</v>
       </c>
     </row>
@@ -3786,7 +4436,7 @@
       <c r="B242" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F242" s="6" t="s">
+      <c r="F242" s="14" t="s">
         <v>103</v>
       </c>
     </row>
@@ -3797,7 +4447,7 @@
       <c r="B243" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F243" s="6" t="s">
+      <c r="F243" s="14" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3844,7 +4494,7 @@
       <c r="C247" t="s">
         <v>8</v>
       </c>
-      <c r="F247" s="6" t="s">
+      <c r="F247" s="14" t="s">
         <v>113</v>
       </c>
     </row>
@@ -3858,7 +4508,7 @@
       <c r="C248" t="s">
         <v>8</v>
       </c>
-      <c r="F248" s="6" t="s">
+      <c r="F248" s="14" t="s">
         <v>106</v>
       </c>
     </row>
@@ -3883,7 +4533,7 @@
       <c r="C250" t="s">
         <v>8</v>
       </c>
-      <c r="F250" s="6" t="s">
+      <c r="F250" s="14" t="s">
         <v>107</v>
       </c>
     </row>
@@ -3897,7 +4547,7 @@
       <c r="C251" t="s">
         <v>8</v>
       </c>
-      <c r="F251" s="6" t="s">
+      <c r="F251" s="14" t="s">
         <v>108</v>
       </c>
     </row>
@@ -3908,8 +4558,8 @@
       <c r="B252" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D252" t="s">
-        <v>48</v>
+      <c r="D252">
+        <v>-9999</v>
       </c>
       <c r="E252" t="s">
         <v>30</v>
@@ -3950,132 +4600,6385 @@
       <c r="C255" t="s">
         <v>8</v>
       </c>
-      <c r="F255" s="6" t="s">
+      <c r="F255" s="14" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="256" spans="1:6" s="9" customFormat="1">
-      <c r="A256" s="9" t="s">
+    <row r="256" spans="1:6" s="6" customFormat="1">
+      <c r="A256" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B256" s="10" t="s">
+      <c r="B256" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C256" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F256" s="11"/>
-    </row>
-    <row r="257" spans="2:2">
-      <c r="B257" s="2"/>
-    </row>
-    <row r="258" spans="2:2">
-      <c r="B258" s="2"/>
-    </row>
-    <row r="259" spans="2:2">
-      <c r="B259" s="2"/>
-    </row>
-    <row r="260" spans="2:2">
-      <c r="B260" s="2"/>
-    </row>
-    <row r="261" spans="2:2">
-      <c r="B261" s="2"/>
-    </row>
-    <row r="262" spans="2:2">
-      <c r="B262" s="2"/>
-    </row>
-    <row r="263" spans="2:2">
-      <c r="B263" s="2"/>
-    </row>
-    <row r="264" spans="2:2">
-      <c r="B264" s="2"/>
-    </row>
-    <row r="265" spans="2:2">
-      <c r="B265" s="2"/>
-    </row>
-    <row r="266" spans="2:2">
-      <c r="B266" s="2"/>
-    </row>
-    <row r="267" spans="2:2">
-      <c r="B267" s="2"/>
-    </row>
-    <row r="268" spans="2:2">
-      <c r="B268" s="2"/>
-    </row>
-    <row r="269" spans="2:2">
-      <c r="B269" s="2"/>
-    </row>
-    <row r="270" spans="2:2">
-      <c r="B270" s="2"/>
-    </row>
-    <row r="271" spans="2:2">
-      <c r="B271" s="2"/>
-    </row>
-    <row r="272" spans="2:2">
-      <c r="B272" s="2"/>
-    </row>
-    <row r="273" spans="2:2">
-      <c r="B273" s="2"/>
-    </row>
-    <row r="274" spans="2:2">
-      <c r="B274" s="2"/>
-    </row>
-    <row r="275" spans="2:2">
-      <c r="B275" s="2"/>
-    </row>
-    <row r="276" spans="2:2">
-      <c r="B276" s="2"/>
-    </row>
-    <row r="277" spans="2:2">
-      <c r="B277" s="2"/>
-    </row>
-    <row r="278" spans="2:2">
-      <c r="B278" s="2"/>
-    </row>
-    <row r="279" spans="2:2">
-      <c r="B279" s="2"/>
-    </row>
-    <row r="280" spans="2:2">
-      <c r="B280" s="2"/>
-    </row>
-    <row r="281" spans="2:2">
-      <c r="B281" s="2"/>
-    </row>
-    <row r="282" spans="2:2">
-      <c r="B282" s="2"/>
-    </row>
-    <row r="283" spans="2:2">
-      <c r="B283" s="2"/>
-    </row>
-    <row r="284" spans="2:2">
-      <c r="B284" s="2"/>
-    </row>
-    <row r="285" spans="2:2">
-      <c r="B285" s="2"/>
-    </row>
-    <row r="286" spans="2:2">
-      <c r="B286" s="2"/>
-    </row>
-    <row r="287" spans="2:2">
-      <c r="B287" s="2"/>
-    </row>
-    <row r="288" spans="2:2">
-      <c r="B288" s="2"/>
-    </row>
-    <row r="289" spans="2:2">
-      <c r="B289" s="2"/>
-    </row>
-    <row r="290" spans="2:2">
-      <c r="B290" s="2"/>
+      <c r="C256" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F256" s="19"/>
+    </row>
+    <row r="257" spans="1:6">
+      <c r="A257" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C257" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
+      <c r="A258" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F258" s="13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
+      <c r="A259" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F259" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
+      <c r="A260" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F260" s="13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
+      <c r="A261" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C261" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
+      <c r="A262" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C262" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
+      <c r="A263" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C263" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
+      <c r="A264" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C264" t="s">
+        <v>8</v>
+      </c>
+      <c r="F264" s="15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
+      <c r="A265" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C265" t="s">
+        <v>8</v>
+      </c>
+      <c r="F265" s="14" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
+      <c r="A266" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C266" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
+      <c r="A267" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C267" t="s">
+        <v>8</v>
+      </c>
+      <c r="F267" s="13" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6">
+      <c r="A268" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C268" t="s">
+        <v>8</v>
+      </c>
+      <c r="F268" s="14" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
+      <c r="A269" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D269">
+        <v>-9999</v>
+      </c>
+      <c r="E269" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6">
+      <c r="A270" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D270">
+        <v>32000</v>
+      </c>
+      <c r="E270" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
+      <c r="A271" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C271" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
+      <c r="A272" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C272" t="s">
+        <v>8</v>
+      </c>
+      <c r="F272" s="14" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" s="10" customFormat="1">
+      <c r="A273" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B273" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C273" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F273" s="21"/>
+    </row>
+    <row r="274" spans="1:6">
+      <c r="A274" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C274" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6">
+      <c r="A275" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F275" s="13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
+      <c r="A276" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F276" s="13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
+      <c r="A277" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F277" s="13" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
+      <c r="A278" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C278" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
+      <c r="A279" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C279" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
+      <c r="A280" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C280" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
+      <c r="A281" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C281" t="s">
+        <v>8</v>
+      </c>
+      <c r="F281" s="22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
+      <c r="A282" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C282" t="s">
+        <v>8</v>
+      </c>
+      <c r="F282" s="14" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
+      <c r="A283" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C283" t="s">
+        <v>8</v>
+      </c>
+      <c r="F283" s="13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
+      <c r="A284" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C284" t="s">
+        <v>35</v>
+      </c>
+      <c r="F284" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6">
+      <c r="A285" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C285" t="s">
+        <v>8</v>
+      </c>
+      <c r="F285" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
+      <c r="A286" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B286" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D286">
+        <v>0</v>
+      </c>
+      <c r="E286" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
+      <c r="A287" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B287" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D287">
+        <v>0</v>
+      </c>
+      <c r="E287" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6">
+      <c r="A288" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B288" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C288" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6">
+      <c r="A289" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C289" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" s="10" customFormat="1">
+      <c r="A290" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B290" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C290" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F290" s="21"/>
+    </row>
+    <row r="291" spans="1:6">
+      <c r="A291" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C291" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6">
+      <c r="A292" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B292" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F292" s="13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6">
+      <c r="A293" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F293" s="22" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6">
+      <c r="A294" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F294" s="22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6">
+      <c r="A295" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B295" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C295" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6">
+      <c r="A296" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C296" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6">
+      <c r="A297" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B297" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C297" t="s">
+        <v>8</v>
+      </c>
+      <c r="F297" s="13" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6">
+      <c r="A298" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C298" t="s">
+        <v>8</v>
+      </c>
+      <c r="F298" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6">
+      <c r="A299" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C299" t="s">
+        <v>8</v>
+      </c>
+      <c r="F299" s="14" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6">
+      <c r="A300" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C300" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6">
+      <c r="A301" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C301" t="s">
+        <v>8</v>
+      </c>
+      <c r="F301" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6">
+      <c r="A302" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C302" t="s">
+        <v>8</v>
+      </c>
+      <c r="F302" s="14" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6">
+      <c r="A303" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D303">
+        <v>24</v>
+      </c>
+      <c r="E303" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6">
+      <c r="A304" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D304">
+        <v>-9999</v>
+      </c>
+      <c r="E304" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6">
+      <c r="A305" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C305" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6">
+      <c r="A306" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C306" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" s="10" customFormat="1">
+      <c r="A307" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B307" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C307" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F307" s="21"/>
+    </row>
+    <row r="308" spans="1:6">
+      <c r="A308" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C308" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6">
+      <c r="A309" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B309" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F309" s="13" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6">
+      <c r="A310" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B310" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F310" s="13" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6">
+      <c r="A311" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B311" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F311" s="22" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6">
+      <c r="A312" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C312" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6">
+      <c r="A313" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B313" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C313" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6">
+      <c r="A314" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C314" t="s">
+        <v>8</v>
+      </c>
+      <c r="F314" s="13" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6">
+      <c r="A315" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B315" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C315" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6">
+      <c r="A316" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B316" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C316" t="s">
+        <v>8</v>
+      </c>
+      <c r="F316" s="13" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6">
+      <c r="A317" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C317" t="s">
+        <v>8</v>
+      </c>
+      <c r="F317" s="22" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6">
+      <c r="A318" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B318" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C318" t="s">
+        <v>8</v>
+      </c>
+      <c r="F318" s="22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6">
+      <c r="A319" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B319" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C319" t="s">
+        <v>8</v>
+      </c>
+      <c r="F319" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6">
+      <c r="A320" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B320" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D320">
+        <v>-9999</v>
+      </c>
+      <c r="E320" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6">
+      <c r="A321" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B321" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D321">
+        <v>32000</v>
+      </c>
+      <c r="E321" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6">
+      <c r="A322" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C322" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6">
+      <c r="A323" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B323" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C323" t="s">
+        <v>8</v>
+      </c>
+      <c r="F323" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" s="10" customFormat="1">
+      <c r="A324" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B324" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C324" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F324" s="21"/>
+    </row>
+    <row r="325" spans="1:6">
+      <c r="A325" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B325" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C325" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6">
+      <c r="A326" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B326" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F326" s="13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6">
+      <c r="A327" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B327" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F327" s="13" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6">
+      <c r="A328" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B328" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F328" s="22" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6">
+      <c r="A329" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B329" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C329" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6">
+      <c r="A330" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B330" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C330" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6">
+      <c r="A331" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B331" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C331" t="s">
+        <v>8</v>
+      </c>
+      <c r="F331" s="13" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6">
+      <c r="A332" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B332" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C332" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6">
+      <c r="A333" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B333" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C333" t="s">
+        <v>8</v>
+      </c>
+      <c r="F333" s="13" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6">
+      <c r="A334" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B334" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C334" t="s">
+        <v>8</v>
+      </c>
+      <c r="F334" s="13" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6">
+      <c r="A335" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B335" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C335" t="s">
+        <v>8</v>
+      </c>
+      <c r="F335" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6">
+      <c r="A336" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B336" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C336" t="s">
+        <v>8</v>
+      </c>
+      <c r="F336" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6">
+      <c r="A337" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B337" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D337">
+        <v>-9999</v>
+      </c>
+      <c r="E337" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6">
+      <c r="A338" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B338" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D338">
+        <v>32000</v>
+      </c>
+      <c r="E338" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6">
+      <c r="A339" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B339" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C339" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6">
+      <c r="A340" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B340" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C340" t="s">
+        <v>8</v>
+      </c>
+      <c r="F340" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" s="10" customFormat="1">
+      <c r="A341" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B341" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C341" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F341" s="21"/>
+    </row>
+    <row r="342" spans="1:6">
+      <c r="A342" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B342" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C342" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6">
+      <c r="A343" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B343" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F343" s="13" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6">
+      <c r="A344" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B344" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F344" s="22" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6">
+      <c r="A345" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B345" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F345" s="22" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6">
+      <c r="A346" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B346" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C346" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6">
+      <c r="A347" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B347" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C347" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6">
+      <c r="A348" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B348" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C348" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6">
+      <c r="A349" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B349" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C349" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6">
+      <c r="A350" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B350" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C350" t="s">
+        <v>8</v>
+      </c>
+      <c r="F350" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6">
+      <c r="A351" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B351" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C351" t="s">
+        <v>8</v>
+      </c>
+      <c r="F351" s="13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6">
+      <c r="A352" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B352" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C352" t="s">
+        <v>8</v>
+      </c>
+      <c r="F352" s="22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6">
+      <c r="A353" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B353" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C353" t="s">
+        <v>8</v>
+      </c>
+      <c r="F353" s="13" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6">
+      <c r="A354" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B354" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D354">
+        <v>256</v>
+      </c>
+      <c r="E354" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6">
+      <c r="A355" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B355" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D355">
+        <v>-9999</v>
+      </c>
+      <c r="E355" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6">
+      <c r="A356" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B356" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C356" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6">
+      <c r="A357" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B357" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C357" t="s">
+        <v>8</v>
+      </c>
+      <c r="F357" s="13" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" s="10" customFormat="1">
+      <c r="A358" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B358" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C358" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F358" s="21"/>
+    </row>
+    <row r="359" spans="1:6">
+      <c r="A359" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B359" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C359" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6">
+      <c r="A360" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B360" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F360" s="13" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6">
+      <c r="A361" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B361" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F361" s="22" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6">
+      <c r="A362" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B362" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F362" s="22" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6">
+      <c r="A363" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B363" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C363" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6">
+      <c r="A364" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C364" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6">
+      <c r="A365" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B365" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C365" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6">
+      <c r="A366" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C366" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6">
+      <c r="A367" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C367" t="s">
+        <v>8</v>
+      </c>
+      <c r="F367" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6">
+      <c r="A368" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B368" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C368" t="s">
+        <v>8</v>
+      </c>
+      <c r="F368" s="13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6">
+      <c r="A369" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B369" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C369" t="s">
+        <v>8</v>
+      </c>
+      <c r="F369" s="13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6">
+      <c r="A370" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B370" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C370" t="s">
+        <v>8</v>
+      </c>
+      <c r="F370" s="13" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6">
+      <c r="A371" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B371" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D371">
+        <v>64</v>
+      </c>
+      <c r="E371" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6">
+      <c r="A372" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B372" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D372">
+        <v>-9999</v>
+      </c>
+      <c r="E372" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6">
+      <c r="A373" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B373" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C373" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6">
+      <c r="A374" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B374" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C374" t="s">
+        <v>8</v>
+      </c>
+      <c r="F374" s="22" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6" s="10" customFormat="1">
+      <c r="A375" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B375" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C375" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F375" s="21"/>
+    </row>
+    <row r="376" spans="1:6">
+      <c r="A376" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B376" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C376" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6">
+      <c r="A377" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B377" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F377" s="13" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6">
+      <c r="A378" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B378" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F378" s="13" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6">
+      <c r="A379" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B379" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F379" s="22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6">
+      <c r="A380" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B380" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C380" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6">
+      <c r="A381" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B381" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C381" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6">
+      <c r="A382" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B382" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C382" t="s">
+        <v>8</v>
+      </c>
+      <c r="F382" s="13" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6">
+      <c r="A383" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B383" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C383" t="s">
+        <v>8</v>
+      </c>
+      <c r="F383" s="13" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6">
+      <c r="A384" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B384" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C384" t="s">
+        <v>8</v>
+      </c>
+      <c r="F384" s="13" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6">
+      <c r="A385" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B385" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C385" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6">
+      <c r="A386" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B386" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C386" t="s">
+        <v>8</v>
+      </c>
+      <c r="F386" s="22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6">
+      <c r="A387" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B387" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C387" t="s">
+        <v>8</v>
+      </c>
+      <c r="F387" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6">
+      <c r="A388" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B388" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D388">
+        <v>336</v>
+      </c>
+      <c r="E388" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6">
+      <c r="A389" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B389" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D389">
+        <v>-9999</v>
+      </c>
+      <c r="E389" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="390" spans="1:6">
+      <c r="A390" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B390" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C390" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="391" spans="1:6">
+      <c r="A391" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B391" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C391" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="392" spans="1:6" s="10" customFormat="1">
+      <c r="A392" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B392" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C392" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F392" s="21"/>
+    </row>
+    <row r="393" spans="1:6">
+      <c r="A393" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B393" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C393" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="394" spans="1:6">
+      <c r="A394" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B394" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F394" s="13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="395" spans="1:6">
+      <c r="A395" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B395" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F395" s="13" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6">
+      <c r="A396" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B396" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F396" s="13" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="397" spans="1:6">
+      <c r="A397" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B397" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C397" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="398" spans="1:6">
+      <c r="A398" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B398" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C398" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="399" spans="1:6">
+      <c r="A399" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B399" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C399" t="s">
+        <v>8</v>
+      </c>
+      <c r="F399" s="13" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="400" spans="1:6">
+      <c r="A400" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B400" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C400" t="s">
+        <v>8</v>
+      </c>
+      <c r="F400" s="22" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="401" spans="1:6">
+      <c r="A401" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B401" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C401" t="s">
+        <v>8</v>
+      </c>
+      <c r="F401" s="22" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="402" spans="1:6">
+      <c r="A402" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B402" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C402" t="s">
+        <v>8</v>
+      </c>
+      <c r="F402" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="403" spans="1:6">
+      <c r="A403" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B403" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C403" t="s">
+        <v>8</v>
+      </c>
+      <c r="F403" s="22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="404" spans="1:6">
+      <c r="A404" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B404" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C404" t="s">
+        <v>8</v>
+      </c>
+      <c r="F404" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="405" spans="1:6">
+      <c r="A405" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B405" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D405">
+        <v>168</v>
+      </c>
+      <c r="E405" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="406" spans="1:6">
+      <c r="A406" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B406" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D406">
+        <v>4000</v>
+      </c>
+      <c r="E406" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="407" spans="1:6">
+      <c r="A407" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B407" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C407" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="408" spans="1:6">
+      <c r="A408" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B408" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C408" t="s">
+        <v>8</v>
+      </c>
+      <c r="F408" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="409" spans="1:6" s="10" customFormat="1">
+      <c r="A409" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B409" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C409" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F409" s="21"/>
+    </row>
+    <row r="410" spans="1:6">
+      <c r="A410" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B410" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C410" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="411" spans="1:6">
+      <c r="A411" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B411" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F411" s="13" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="412" spans="1:6">
+      <c r="A412" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B412" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F412" s="13" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="413" spans="1:6">
+      <c r="A413" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B413" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F413" s="13" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="414" spans="1:6">
+      <c r="A414" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B414" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C414" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="415" spans="1:6">
+      <c r="A415" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B415" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C415" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="416" spans="1:6">
+      <c r="A416" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B416" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C416" t="s">
+        <v>8</v>
+      </c>
+      <c r="F416" s="13" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="417" spans="1:6">
+      <c r="A417" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B417" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C417" t="s">
+        <v>8</v>
+      </c>
+      <c r="F417" s="22" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="418" spans="1:6">
+      <c r="A418" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B418" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C418" t="s">
+        <v>8</v>
+      </c>
+      <c r="F418" s="22" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="419" spans="1:6">
+      <c r="A419" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B419" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C419" t="s">
+        <v>8</v>
+      </c>
+      <c r="F419" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="420" spans="1:6">
+      <c r="A420" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B420" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C420" t="s">
+        <v>8</v>
+      </c>
+      <c r="F420" s="22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="421" spans="1:6">
+      <c r="A421" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B421" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C421" t="s">
+        <v>8</v>
+      </c>
+      <c r="F421" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="422" spans="1:6">
+      <c r="A422" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B422" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D422">
+        <v>168</v>
+      </c>
+      <c r="E422" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="423" spans="1:6">
+      <c r="A423" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B423" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D423">
+        <v>4000</v>
+      </c>
+      <c r="E423" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="424" spans="1:6">
+      <c r="A424" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B424" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C424" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="425" spans="1:6">
+      <c r="A425" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B425" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C425" t="s">
+        <v>8</v>
+      </c>
+      <c r="F425" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="426" spans="1:6" s="10" customFormat="1">
+      <c r="A426" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B426" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C426" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F426" s="21"/>
+    </row>
+    <row r="427" spans="1:6">
+      <c r="A427" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B427" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C427" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="428" spans="1:6">
+      <c r="A428" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B428" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F428" s="24" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="429" spans="1:6">
+      <c r="A429" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B429" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F429" s="25" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="430" spans="1:6">
+      <c r="A430" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B430" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F430" s="13" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="431" spans="1:6">
+      <c r="A431" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B431" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C431" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="432" spans="1:6">
+      <c r="A432" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B432" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C432" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="433" spans="1:6">
+      <c r="A433" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B433" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C433" t="s">
+        <v>8</v>
+      </c>
+      <c r="F433" s="13" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="434" spans="1:6">
+      <c r="A434" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B434" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C434" t="s">
+        <v>8</v>
+      </c>
+      <c r="F434" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="435" spans="1:6">
+      <c r="A435" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B435" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C435" t="s">
+        <v>8</v>
+      </c>
+      <c r="F435" s="26" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="436" spans="1:6">
+      <c r="A436" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B436" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C436" t="s">
+        <v>8</v>
+      </c>
+      <c r="F436" s="27" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="437" spans="1:6">
+      <c r="A437" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B437" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C437" t="s">
+        <v>8</v>
+      </c>
+      <c r="F437" s="22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="438" spans="1:6">
+      <c r="A438" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B438" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C438" t="s">
+        <v>8</v>
+      </c>
+      <c r="F438" s="13" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="439" spans="1:6">
+      <c r="A439" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B439" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D439">
+        <v>200</v>
+      </c>
+      <c r="E439" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="440" spans="1:6">
+      <c r="A440" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B440" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D440">
+        <v>4000</v>
+      </c>
+      <c r="E440" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="441" spans="1:6">
+      <c r="A441" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B441" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C441" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="442" spans="1:6">
+      <c r="A442" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B442" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C442" t="s">
+        <v>8</v>
+      </c>
+      <c r="F442" s="13" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="443" spans="1:6" s="10" customFormat="1">
+      <c r="A443" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B443" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C443" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F443" s="21"/>
+    </row>
+    <row r="444" spans="1:6">
+      <c r="A444" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B444" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C444" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="445" spans="1:6">
+      <c r="A445" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B445" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F445" s="24" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="446" spans="1:6">
+      <c r="A446" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B446" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F446" s="25" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="447" spans="1:6">
+      <c r="A447" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B447" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F447" s="13" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="448" spans="1:6">
+      <c r="A448" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B448" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C448" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="449" spans="1:6">
+      <c r="A449" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B449" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C449" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="450" spans="1:6">
+      <c r="A450" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B450" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C450" t="s">
+        <v>8</v>
+      </c>
+      <c r="F450" s="13" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="451" spans="1:6">
+      <c r="A451" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B451" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C451" t="s">
+        <v>8</v>
+      </c>
+      <c r="F451" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="452" spans="1:6">
+      <c r="A452" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B452" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C452" t="s">
+        <v>8</v>
+      </c>
+      <c r="F452" s="26" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="453" spans="1:6">
+      <c r="A453" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B453" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C453" t="s">
+        <v>8</v>
+      </c>
+      <c r="F453" s="27" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="454" spans="1:6">
+      <c r="A454" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B454" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C454" t="s">
+        <v>8</v>
+      </c>
+      <c r="F454" s="13" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="455" spans="1:6">
+      <c r="A455" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B455" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C455" t="s">
+        <v>8</v>
+      </c>
+      <c r="F455" s="13" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="456" spans="1:6">
+      <c r="A456" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B456" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D456">
+        <v>264</v>
+      </c>
+      <c r="E456" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="457" spans="1:6">
+      <c r="A457" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B457" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D457">
+        <v>4000</v>
+      </c>
+      <c r="E457" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="458" spans="1:6">
+      <c r="A458" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B458" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C458" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="459" spans="1:6">
+      <c r="A459" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B459" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C459" t="s">
+        <v>8</v>
+      </c>
+      <c r="F459" s="13" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="460" spans="1:6" s="10" customFormat="1">
+      <c r="A460" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B460" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C460" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F460" s="21"/>
+    </row>
+    <row r="461" spans="1:6">
+      <c r="A461" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B461" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C461" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="462" spans="1:6">
+      <c r="A462" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B462" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F462" s="27" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="463" spans="1:6">
+      <c r="A463" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B463" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F463" s="27" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="464" spans="1:6">
+      <c r="A464" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B464" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F464" s="27" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="465" spans="1:6">
+      <c r="A465" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B465" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C465" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="466" spans="1:6">
+      <c r="A466" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B466" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C466" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="467" spans="1:6">
+      <c r="A467" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B467" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C467" t="s">
+        <v>8</v>
+      </c>
+      <c r="F467" s="27" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="468" spans="1:6">
+      <c r="A468" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B468" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C468" t="s">
+        <v>8</v>
+      </c>
+      <c r="F468" s="27" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="469" spans="1:6">
+      <c r="A469" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B469" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C469" t="s">
+        <v>8</v>
+      </c>
+      <c r="F469" s="26" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="470" spans="1:6">
+      <c r="A470" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B470" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C470" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="471" spans="1:6">
+      <c r="A471" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B471" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C471" t="s">
+        <v>8</v>
+      </c>
+      <c r="F471" s="27" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="472" spans="1:6">
+      <c r="A472" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B472" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C472" t="s">
+        <v>8</v>
+      </c>
+      <c r="F472" s="27" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="473" spans="1:6">
+      <c r="A473" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B473" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D473">
+        <v>336</v>
+      </c>
+      <c r="E473" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="474" spans="1:6">
+      <c r="A474" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B474" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D474">
+        <v>-9999</v>
+      </c>
+      <c r="E474" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="475" spans="1:6">
+      <c r="A475" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B475" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C475" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="476" spans="1:6">
+      <c r="A476" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B476" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C476" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="477" spans="1:6" s="10" customFormat="1">
+      <c r="A477" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B477" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C477" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F477" s="21"/>
+    </row>
+    <row r="478" spans="1:6">
+      <c r="A478" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B478" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C478" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="479" spans="1:6">
+      <c r="A479" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B479" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F479" s="27" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="480" spans="1:6">
+      <c r="A480" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B480" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F480" s="27" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="481" spans="1:6">
+      <c r="A481" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B481" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F481" s="26" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="482" spans="1:6">
+      <c r="A482" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B482" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C482" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="483" spans="1:6">
+      <c r="A483" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B483" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C483" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="484" spans="1:6">
+      <c r="A484" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B484" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C484" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="485" spans="1:6">
+      <c r="A485" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B485" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C485" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="486" spans="1:6">
+      <c r="A486" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B486" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C486" t="s">
+        <v>8</v>
+      </c>
+      <c r="F486" s="26" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="487" spans="1:6">
+      <c r="A487" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B487" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C487" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="488" spans="1:6">
+      <c r="A488" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B488" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C488" t="s">
+        <v>8</v>
+      </c>
+      <c r="F488" s="27" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="489" spans="1:6">
+      <c r="A489" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B489" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C489" t="s">
+        <v>8</v>
+      </c>
+      <c r="F489" s="27" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="490" spans="1:6">
+      <c r="A490" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B490" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D490">
+        <v>72</v>
+      </c>
+      <c r="E490" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="491" spans="1:6">
+      <c r="A491" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B491" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D491">
+        <v>-9999</v>
+      </c>
+      <c r="E491" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="492" spans="1:6">
+      <c r="A492" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B492" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C492" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="493" spans="1:6">
+      <c r="A493" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B493" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C493" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="494" spans="1:6" s="10" customFormat="1">
+      <c r="A494" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B494" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C494" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F494" s="21"/>
+    </row>
+    <row r="495" spans="1:6">
+      <c r="A495" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B495" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C495" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="496" spans="1:6">
+      <c r="A496" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B496" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F496" s="13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="497" spans="1:6">
+      <c r="A497" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B497" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F497" s="13" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="498" spans="1:6">
+      <c r="A498" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B498" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F498" s="22" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="499" spans="1:6">
+      <c r="A499" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B499" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C499" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="500" spans="1:6">
+      <c r="A500" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B500" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C500" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="501" spans="1:6">
+      <c r="A501" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B501" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C501" t="s">
+        <v>8</v>
+      </c>
+      <c r="F501" s="28" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="502" spans="1:6">
+      <c r="A502" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B502" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C502" t="s">
+        <v>8</v>
+      </c>
+      <c r="F502" s="28" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="503" spans="1:6">
+      <c r="A503" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B503" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C503" t="s">
+        <v>8</v>
+      </c>
+      <c r="F503" s="22" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="504" spans="1:6">
+      <c r="A504" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B504" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C504" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="505" spans="1:6">
+      <c r="A505" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B505" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C505" t="s">
+        <v>8</v>
+      </c>
+      <c r="F505" s="13" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="506" spans="1:6">
+      <c r="A506" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B506" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C506" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="507" spans="1:6">
+      <c r="A507" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B507" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D507">
+        <v>240</v>
+      </c>
+      <c r="E507" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="508" spans="1:6">
+      <c r="A508" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B508" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D508">
+        <v>-9999</v>
+      </c>
+      <c r="E508" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="509" spans="1:6">
+      <c r="A509" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B509" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C509" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="510" spans="1:6">
+      <c r="A510" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B510" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C510" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="511" spans="1:6" s="10" customFormat="1">
+      <c r="A511" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B511" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C511" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F511" s="21"/>
+    </row>
+    <row r="512" spans="1:6">
+      <c r="A512" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B512" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C512" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="513" spans="1:6">
+      <c r="A513" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B513" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F513" s="14" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="514" spans="1:6">
+      <c r="A514" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B514" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F514" s="14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="515" spans="1:6">
+      <c r="A515" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B515" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F515" s="14" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="516" spans="1:6">
+      <c r="A516" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B516" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C516" t="s">
+        <v>8</v>
+      </c>
+      <c r="F516" s="14" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="517" spans="1:6">
+      <c r="A517" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B517" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C517" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="518" spans="1:6">
+      <c r="A518" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B518" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C518" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="519" spans="1:6">
+      <c r="A519" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B519" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C519" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="520" spans="1:6">
+      <c r="A520" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B520" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C520" t="s">
+        <v>8</v>
+      </c>
+      <c r="F520" s="14" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="521" spans="1:6">
+      <c r="A521" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B521" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C521" t="s">
+        <v>8</v>
+      </c>
+      <c r="F521" s="14" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="522" spans="1:6">
+      <c r="A522" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B522" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C522" t="s">
+        <v>8</v>
+      </c>
+      <c r="F522" s="14" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="523" spans="1:6">
+      <c r="A523" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B523" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C523" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="524" spans="1:6">
+      <c r="A524" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B524" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D524">
+        <v>336</v>
+      </c>
+      <c r="E524" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="525" spans="1:6">
+      <c r="A525" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B525" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D525">
+        <v>4000</v>
+      </c>
+      <c r="E525" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="526" spans="1:6">
+      <c r="A526" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B526" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C526" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="527" spans="1:6">
+      <c r="A527" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B527" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C527" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="528" spans="1:6">
+      <c r="A528" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="B528" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C528" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D528" s="10"/>
+      <c r="E528" s="10"/>
+      <c r="F528" s="21"/>
+    </row>
+    <row r="529" spans="1:6">
+      <c r="A529" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B529" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C529" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="530" spans="1:6">
+      <c r="A530" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B530" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F530" s="14" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="531" spans="1:6">
+      <c r="A531" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B531" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F531" s="14" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="532" spans="1:6">
+      <c r="A532" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B532" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C532" t="s">
+        <v>8</v>
+      </c>
+      <c r="F532" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="533" spans="1:6">
+      <c r="A533" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B533" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C533" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="534" spans="1:6">
+      <c r="A534" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B534" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C534" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="535" spans="1:6">
+      <c r="A535" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B535" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C535" t="s">
+        <v>8</v>
+      </c>
+      <c r="F535" s="14" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="536" spans="1:6">
+      <c r="A536" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B536" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C536" t="s">
+        <v>8</v>
+      </c>
+      <c r="F536" s="14" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="537" spans="1:6">
+      <c r="A537" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B537" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C537" t="s">
+        <v>8</v>
+      </c>
+      <c r="F537" s="14" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="538" spans="1:6">
+      <c r="A538" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B538" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C538" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="539" spans="1:6">
+      <c r="A539" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B539" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C539" t="s">
+        <v>8</v>
+      </c>
+      <c r="F539" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="540" spans="1:6">
+      <c r="A540" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B540" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C540" t="s">
+        <v>8</v>
+      </c>
+      <c r="F540" s="14" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="541" spans="1:6">
+      <c r="A541" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B541" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D541">
+        <v>-9999</v>
+      </c>
+      <c r="E541" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="542" spans="1:6">
+      <c r="A542" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B542" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D542">
+        <v>-9999</v>
+      </c>
+      <c r="E542" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="543" spans="1:6">
+      <c r="A543" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B543" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C543" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="544" spans="1:6">
+      <c r="A544" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B544" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C544" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="545" spans="1:6">
+      <c r="A545" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="B545" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C545" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D545" s="10"/>
+      <c r="E545" s="10"/>
+      <c r="F545" s="21"/>
+    </row>
+    <row r="546" spans="1:6">
+      <c r="A546" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B546" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C546" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="547" spans="1:6">
+      <c r="A547" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B547" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F547" s="14" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="548" spans="1:6">
+      <c r="A548" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B548" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F548" s="14" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="549" spans="1:6">
+      <c r="A549" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B549" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C549" t="s">
+        <v>8</v>
+      </c>
+      <c r="F549" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="550" spans="1:6">
+      <c r="A550" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B550" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C550" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="551" spans="1:6">
+      <c r="A551" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B551" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C551" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="552" spans="1:6">
+      <c r="A552" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B552" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C552" t="s">
+        <v>8</v>
+      </c>
+      <c r="F552" s="14" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="553" spans="1:6">
+      <c r="A553" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B553" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C553" t="s">
+        <v>8</v>
+      </c>
+      <c r="F553" s="14" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="554" spans="1:6">
+      <c r="A554" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B554" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C554" t="s">
+        <v>8</v>
+      </c>
+      <c r="F554" s="14" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="555" spans="1:6">
+      <c r="A555" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B555" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C555" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="556" spans="1:6">
+      <c r="A556" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B556" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C556" t="s">
+        <v>8</v>
+      </c>
+      <c r="F556" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="557" spans="1:6">
+      <c r="A557" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B557" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C557" t="s">
+        <v>8</v>
+      </c>
+      <c r="F557" s="14" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="558" spans="1:6">
+      <c r="A558" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B558" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D558">
+        <v>168</v>
+      </c>
+      <c r="E558" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="559" spans="1:6">
+      <c r="A559" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B559" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D559">
+        <v>-9999</v>
+      </c>
+      <c r="E559" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="560" spans="1:6">
+      <c r="A560" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B560" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C560" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="561" spans="1:6">
+      <c r="A561" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B561" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C561" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="562" spans="1:6">
+      <c r="A562" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="B562" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C562" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D562" s="10"/>
+      <c r="E562" s="10"/>
+      <c r="F562" s="21"/>
+    </row>
+    <row r="563" spans="1:6">
+      <c r="A563" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B563" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C563" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="564" spans="1:6">
+      <c r="A564" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B564" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F564" s="14" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="565" spans="1:6">
+      <c r="A565" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B565" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F565" s="14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="566" spans="1:6">
+      <c r="A566" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B566" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C566" t="s">
+        <v>8</v>
+      </c>
+      <c r="F566" s="14" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="567" spans="1:6">
+      <c r="A567" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B567" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C567" t="s">
+        <v>8</v>
+      </c>
+      <c r="F567" s="14" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="568" spans="1:6">
+      <c r="A568" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B568" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C568" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="569" spans="1:6">
+      <c r="A569" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B569" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C569" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="570" spans="1:6">
+      <c r="A570" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B570" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C570" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="571" spans="1:6">
+      <c r="A571" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B571" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C571" t="s">
+        <v>8</v>
+      </c>
+      <c r="F571" s="14" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="572" spans="1:6">
+      <c r="A572" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B572" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C572" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="573" spans="1:6">
+      <c r="A573" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B573" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C573" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="574" spans="1:6">
+      <c r="A574" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B574" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C574" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="575" spans="1:6">
+      <c r="A575" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B575" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D575">
+        <v>-9999</v>
+      </c>
+      <c r="E575" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="576" spans="1:6">
+      <c r="A576" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B576" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D576">
+        <v>-9999</v>
+      </c>
+      <c r="E576" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="577" spans="1:6">
+      <c r="A577" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B577" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C577" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="578" spans="1:6">
+      <c r="A578" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B578" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C578" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="579" spans="1:6">
+      <c r="A579" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="B579" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C579" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D579" s="10"/>
+      <c r="E579" s="10"/>
+      <c r="F579" s="21"/>
+    </row>
+    <row r="580" spans="1:6">
+      <c r="A580" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B580" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C580" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="581" spans="1:6">
+      <c r="A581" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B581" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F581" s="14" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="582" spans="1:6">
+      <c r="A582" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B582" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F582" s="14" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="583" spans="1:6">
+      <c r="A583" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B583" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C583" t="s">
+        <v>8</v>
+      </c>
+      <c r="F583" s="14" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="584" spans="1:6">
+      <c r="A584" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B584" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C584" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="585" spans="1:6">
+      <c r="A585" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B585" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C585" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="586" spans="1:6">
+      <c r="A586" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B586" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C586" t="s">
+        <v>8</v>
+      </c>
+      <c r="F586" s="14" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="587" spans="1:6">
+      <c r="A587" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B587" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C587" t="s">
+        <v>8</v>
+      </c>
+      <c r="F587" s="14" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="588" spans="1:6">
+      <c r="A588" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B588" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C588" t="s">
+        <v>8</v>
+      </c>
+      <c r="F588" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="589" spans="1:6">
+      <c r="A589" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B589" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C589" t="s">
+        <v>8</v>
+      </c>
+      <c r="F589" s="14" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="590" spans="1:6">
+      <c r="A590" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B590" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C590" t="s">
+        <v>8</v>
+      </c>
+      <c r="F590" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="591" spans="1:6">
+      <c r="A591" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B591" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C591" t="s">
+        <v>8</v>
+      </c>
+      <c r="F591" s="14" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="592" spans="1:6">
+      <c r="A592" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B592" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D592">
+        <v>339</v>
+      </c>
+      <c r="E592" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="593" spans="1:6">
+      <c r="A593" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B593" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D593">
+        <v>-9999</v>
+      </c>
+      <c r="E593" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="594" spans="1:6">
+      <c r="A594" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B594" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C594" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="595" spans="1:6">
+      <c r="A595" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B595" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C595" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="596" spans="1:6">
+      <c r="A596" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="B596" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C596" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D596" s="10"/>
+      <c r="E596" s="10"/>
+      <c r="F596" s="21"/>
+    </row>
+    <row r="597" spans="1:6">
+      <c r="A597" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B597" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C597" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="598" spans="1:6">
+      <c r="A598" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B598" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F598" s="14" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="599" spans="1:6">
+      <c r="A599" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B599" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F599" s="14" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="600" spans="1:6">
+      <c r="A600" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B600" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C600" t="s">
+        <v>8</v>
+      </c>
+      <c r="F600" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="601" spans="1:6">
+      <c r="A601" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B601" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C601" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="602" spans="1:6">
+      <c r="A602" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B602" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C602" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="603" spans="1:6">
+      <c r="A603" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B603" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C603" t="s">
+        <v>8</v>
+      </c>
+      <c r="F603" s="14" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="604" spans="1:6">
+      <c r="A604" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B604" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C604" t="s">
+        <v>8</v>
+      </c>
+      <c r="F604" s="14" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="605" spans="1:6">
+      <c r="A605" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B605" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C605" t="s">
+        <v>8</v>
+      </c>
+      <c r="F605" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="606" spans="1:6">
+      <c r="A606" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B606" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C606" t="s">
+        <v>8</v>
+      </c>
+      <c r="F606" s="14" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="607" spans="1:6">
+      <c r="A607" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B607" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C607" t="s">
+        <v>8</v>
+      </c>
+      <c r="F607" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="608" spans="1:6">
+      <c r="A608" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B608" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C608" t="s">
+        <v>8</v>
+      </c>
+      <c r="F608" s="14" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="609" spans="1:6">
+      <c r="A609" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B609" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D609">
+        <v>339</v>
+      </c>
+      <c r="E609" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="610" spans="1:6">
+      <c r="A610" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B610" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D610">
+        <v>-9999</v>
+      </c>
+      <c r="E610" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="611" spans="1:6">
+      <c r="A611" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B611" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C611" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="612" spans="1:6">
+      <c r="A612" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B612" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C612" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="613" spans="1:6">
+      <c r="A613" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="B613" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C613" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D613" s="10"/>
+      <c r="E613" s="10"/>
+      <c r="F613" s="21"/>
+    </row>
+    <row r="614" spans="1:6">
+      <c r="A614" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B614" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C614" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="615" spans="1:6">
+      <c r="A615" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B615" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F615" s="14" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="616" spans="1:6">
+      <c r="A616" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B616" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F616" s="14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="617" spans="1:6">
+      <c r="A617" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B617" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C617" t="s">
+        <v>8</v>
+      </c>
+      <c r="F617" s="22" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="618" spans="1:6">
+      <c r="A618" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B618" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C618" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="619" spans="1:6">
+      <c r="A619" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B619" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C619" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="620" spans="1:6">
+      <c r="A620" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B620" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C620" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="621" spans="1:6">
+      <c r="A621" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B621" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C621" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="622" spans="1:6">
+      <c r="A622" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B622" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C622" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="623" spans="1:6">
+      <c r="A623" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B623" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C623" t="s">
+        <v>8</v>
+      </c>
+      <c r="F623" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="624" spans="1:6">
+      <c r="A624" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B624" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C624" t="s">
+        <v>8</v>
+      </c>
+      <c r="F624" s="14" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="625" spans="1:6">
+      <c r="A625" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B625" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C625" t="s">
+        <v>8</v>
+      </c>
+      <c r="F625" s="14" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="626" spans="1:6">
+      <c r="A626" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B626" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="627" spans="1:6">
+      <c r="A627" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B627" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D627">
+        <v>100</v>
+      </c>
+      <c r="E627" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="628" spans="1:6">
+      <c r="A628" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B628" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C628" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="629" spans="1:6">
+      <c r="A629" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B629" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C629" t="s">
+        <v>8</v>
+      </c>
+      <c r="F629" s="14" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="630" spans="1:6">
+      <c r="A630" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="B630" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C630" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D630" s="10"/>
+      <c r="E630" s="10"/>
+      <c r="F630" s="21"/>
+    </row>
+    <row r="631" spans="1:6">
+      <c r="A631" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B631" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C631" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="632" spans="1:6">
+      <c r="A632" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B632" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F632" s="14" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="633" spans="1:6">
+      <c r="A633" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B633" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F633" s="14" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="634" spans="1:6">
+      <c r="A634" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B634" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C634" t="s">
+        <v>8</v>
+      </c>
+      <c r="F634" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="635" spans="1:6">
+      <c r="A635" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B635" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C635" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="636" spans="1:6">
+      <c r="A636" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B636" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C636" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="637" spans="1:6">
+      <c r="A637" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B637" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C637" t="s">
+        <v>8</v>
+      </c>
+      <c r="F637" s="14" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="638" spans="1:6">
+      <c r="A638" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B638" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C638" t="s">
+        <v>8</v>
+      </c>
+      <c r="F638" s="14" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="639" spans="1:6">
+      <c r="A639" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B639" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C639" t="s">
+        <v>8</v>
+      </c>
+      <c r="F639" s="14" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="640" spans="1:6">
+      <c r="A640" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B640" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C640" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="641" spans="1:6">
+      <c r="A641" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B641" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C641" t="s">
+        <v>8</v>
+      </c>
+      <c r="F641" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="642" spans="1:6">
+      <c r="A642" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B642" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C642" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="643" spans="1:6">
+      <c r="A643" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B643" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D643">
+        <v>24</v>
+      </c>
+      <c r="E643" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="644" spans="1:6">
+      <c r="A644" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B644" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D644">
+        <v>-9999</v>
+      </c>
+      <c r="E644" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="645" spans="1:6">
+      <c r="A645" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B645" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C645" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="646" spans="1:6">
+      <c r="A646" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B646" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C646" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="647" spans="1:6">
+      <c r="A647" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="B647" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C647" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D647" s="10"/>
+      <c r="E647" s="10"/>
+      <c r="F647" s="21"/>
+    </row>
+    <row r="648" spans="1:6">
+      <c r="A648" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B648" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C648" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="649" spans="1:6">
+      <c r="A649" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B649" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F649" s="14" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="650" spans="1:6">
+      <c r="A650" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B650" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F650" s="14" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="651" spans="1:6">
+      <c r="A651" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B651" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C651" t="s">
+        <v>8</v>
+      </c>
+      <c r="F651" s="14" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="652" spans="1:6">
+      <c r="A652" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B652" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C652" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="653" spans="1:6">
+      <c r="A653" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B653" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C653" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="654" spans="1:6">
+      <c r="A654" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B654" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C654" t="s">
+        <v>8</v>
+      </c>
+      <c r="F654" s="14" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="655" spans="1:6">
+      <c r="A655" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B655" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C655" t="s">
+        <v>8</v>
+      </c>
+      <c r="F655" s="14" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="656" spans="1:6">
+      <c r="A656" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B656" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C656" t="s">
+        <v>8</v>
+      </c>
+      <c r="F656" s="14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="657" spans="1:6">
+      <c r="A657" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B657" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C657" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="658" spans="1:6">
+      <c r="A658" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B658" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C658" t="s">
+        <v>8</v>
+      </c>
+      <c r="F658" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="659" spans="1:6">
+      <c r="A659" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B659" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C659" t="s">
+        <v>8</v>
+      </c>
+      <c r="F659" s="14" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="660" spans="1:6">
+      <c r="A660" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B660" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D660">
+        <v>-9999</v>
+      </c>
+      <c r="E660" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="661" spans="1:6">
+      <c r="A661" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B661" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D661">
+        <v>-9999</v>
+      </c>
+      <c r="E661" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="662" spans="1:6">
+      <c r="A662" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B662" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C662" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="663" spans="1:6">
+      <c r="A663" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B663" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C663" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="664" spans="1:6">
+      <c r="A664" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="B664" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C664" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D664" s="10"/>
+      <c r="E664" s="10"/>
+      <c r="F664" s="21"/>
+    </row>
+    <row r="665" spans="1:6">
+      <c r="A665" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B665" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C665" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="666" spans="1:6">
+      <c r="A666" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B666" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F666" s="14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="667" spans="1:6">
+      <c r="A667" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B667" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F667" s="14" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="668" spans="1:6">
+      <c r="A668" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B668" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C668" t="s">
+        <v>8</v>
+      </c>
+      <c r="F668" s="14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="669" spans="1:6">
+      <c r="A669" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B669" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C669" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="670" spans="1:6">
+      <c r="A670" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B670" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C670" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="671" spans="1:6">
+      <c r="A671" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B671" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C671" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="672" spans="1:6">
+      <c r="A672" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B672" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C672" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="673" spans="1:6">
+      <c r="A673" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B673" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C673" t="s">
+        <v>8</v>
+      </c>
+      <c r="F673" s="14" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="674" spans="1:6">
+      <c r="A674" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B674" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C674" t="s">
+        <v>8</v>
+      </c>
+      <c r="F674" s="14" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="675" spans="1:6">
+      <c r="A675" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B675" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C675" t="s">
+        <v>8</v>
+      </c>
+      <c r="F675" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="676" spans="1:6">
+      <c r="A676" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B676" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C676" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="677" spans="1:6">
+      <c r="A677" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B677" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D677">
+        <v>-9999</v>
+      </c>
+      <c r="E677" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="678" spans="1:6">
+      <c r="A678" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B678" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D678">
+        <v>64</v>
+      </c>
+      <c r="E678" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="679" spans="1:6">
+      <c r="A679" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B679" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C679" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="680" spans="1:6">
+      <c r="A680" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B680" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C680" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="681" spans="1:6">
+      <c r="A681" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="B681" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C681" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D681" s="10"/>
+      <c r="E681" s="10"/>
+      <c r="F681" s="21"/>
+    </row>
+    <row r="682" spans="1:6">
+      <c r="A682" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B682" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C682" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="683" spans="1:6">
+      <c r="A683" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B683" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F683" s="29" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="684" spans="1:6">
+      <c r="A684" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B684" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F684" s="14" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="685" spans="1:6">
+      <c r="A685" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B685" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C685" t="s">
+        <v>8</v>
+      </c>
+      <c r="F685" s="14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="686" spans="1:6">
+      <c r="A686" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B686" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C686" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="687" spans="1:6">
+      <c r="A687" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B687" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C687" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="688" spans="1:6">
+      <c r="A688" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B688" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C688" t="s">
+        <v>8</v>
+      </c>
+      <c r="F688" s="14" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="689" spans="1:6">
+      <c r="A689" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B689" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C689" t="s">
+        <v>8</v>
+      </c>
+      <c r="F689" s="14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="690" spans="1:6">
+      <c r="A690" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B690" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C690" t="s">
+        <v>8</v>
+      </c>
+      <c r="F690" s="14" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="691" spans="1:6">
+      <c r="A691" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B691" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C691" t="s">
+        <v>8</v>
+      </c>
+      <c r="F691" s="14" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="692" spans="1:6">
+      <c r="A692" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B692" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C692" t="s">
+        <v>8</v>
+      </c>
+      <c r="F692" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="693" spans="1:6">
+      <c r="A693" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B693" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C693" t="s">
+        <v>8</v>
+      </c>
+      <c r="F693" s="14" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="694" spans="1:6">
+      <c r="A694" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B694" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D694">
+        <v>-9999</v>
+      </c>
+      <c r="E694" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="695" spans="1:6">
+      <c r="A695" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B695" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D695">
+        <v>64</v>
+      </c>
+      <c r="E695" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="696" spans="1:6">
+      <c r="A696" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B696" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C696" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="697" spans="1:6">
+      <c r="A697" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B697" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C697" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="698" spans="1:6">
+      <c r="A698" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="B698" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C698" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D698" s="10"/>
+      <c r="E698" s="10"/>
+      <c r="F698" s="21"/>
+    </row>
+    <row r="699" spans="1:6">
+      <c r="A699" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B699" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C699" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="700" spans="1:6">
+      <c r="A700" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B700" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F700" s="14" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="701" spans="1:6">
+      <c r="A701" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B701" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F701" s="14" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="702" spans="1:6">
+      <c r="A702" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B702" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C702" t="s">
+        <v>8</v>
+      </c>
+      <c r="F702" s="14" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="703" spans="1:6">
+      <c r="A703" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B703" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C703" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="704" spans="1:6">
+      <c r="A704" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B704" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C704" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="705" spans="1:6">
+      <c r="A705" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B705" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C705" t="s">
+        <v>8</v>
+      </c>
+      <c r="F705" s="14" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="706" spans="1:6">
+      <c r="A706" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B706" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C706" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="707" spans="1:6">
+      <c r="A707" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B707" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C707" t="s">
+        <v>8</v>
+      </c>
+      <c r="F707" s="14" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="708" spans="1:6">
+      <c r="A708" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B708" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C708" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="709" spans="1:6">
+      <c r="A709" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B709" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C709" t="s">
+        <v>8</v>
+      </c>
+      <c r="F709" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="710" spans="1:6">
+      <c r="A710" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B710" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C710" t="s">
+        <v>8</v>
+      </c>
+      <c r="F710" s="14" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="711" spans="1:6">
+      <c r="A711" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B711" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D711">
+        <v>-9999</v>
+      </c>
+      <c r="E711" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="712" spans="1:6">
+      <c r="A712" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B712" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D712">
+        <v>8000</v>
+      </c>
+      <c r="E712" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="713" spans="1:6">
+      <c r="A713" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B713" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C713" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="714" spans="1:6">
+      <c r="A714" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B714" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C714" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="715" spans="1:6">
+      <c r="A715" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="B715" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C715" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D715" s="10"/>
+      <c r="E715" s="10"/>
+      <c r="F715" s="21" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="716" spans="1:6">
+      <c r="A716" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B716" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C716" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="717" spans="1:6">
+      <c r="A717" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B717" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F717" s="14" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="718" spans="1:6">
+      <c r="A718" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B718" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F718" s="14" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="719" spans="1:6">
+      <c r="A719" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B719" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C719" t="s">
+        <v>8</v>
+      </c>
+      <c r="F719" s="13" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="720" spans="1:6">
+      <c r="A720" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B720" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C720" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="721" spans="1:6">
+      <c r="A721" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B721" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C721" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="722" spans="1:6">
+      <c r="A722" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B722" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C722" t="s">
+        <v>8</v>
+      </c>
+      <c r="F722" s="14" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="723" spans="1:6">
+      <c r="A723" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B723" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C723" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="724" spans="1:6">
+      <c r="A724" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B724" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C724" t="s">
+        <v>8</v>
+      </c>
+      <c r="F724" s="14" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="725" spans="1:6">
+      <c r="A725" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B725" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C725" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="726" spans="1:6">
+      <c r="A726" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B726" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C726" t="s">
+        <v>8</v>
+      </c>
+      <c r="F726" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="727" spans="1:6">
+      <c r="A727" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B727" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="728" spans="1:6">
+      <c r="A728" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B728" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D728">
+        <v>-9999</v>
+      </c>
+      <c r="E728" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="729" spans="1:6">
+      <c r="A729" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B729" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D729">
+        <v>32000</v>
+      </c>
+      <c r="E729" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="730" spans="1:6">
+      <c r="A730" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B730" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C730" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="731" spans="1:6">
+      <c r="A731" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B731" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C731" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="732" spans="1:6">
+      <c r="A732" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="B732" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C732" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D732" s="10"/>
+      <c r="E732" s="10"/>
+      <c r="F732" s="21"/>
+    </row>
+    <row r="733" spans="1:6">
+      <c r="A733" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B733" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C733" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="734" spans="1:6">
+      <c r="A734" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B734" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F734" s="14" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="735" spans="1:6">
+      <c r="A735" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B735" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F735" s="14" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="736" spans="1:6">
+      <c r="A736" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B736" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C736" t="s">
+        <v>8</v>
+      </c>
+      <c r="F736" s="13" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="737" spans="1:6">
+      <c r="A737" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B737" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C737" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="738" spans="1:6">
+      <c r="A738" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B738" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C738" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="739" spans="1:6">
+      <c r="A739" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B739" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C739" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="740" spans="1:6">
+      <c r="A740" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B740" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C740" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="741" spans="1:6">
+      <c r="A741" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B741" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C741" t="s">
+        <v>8</v>
+      </c>
+      <c r="F741" s="14" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="742" spans="1:6">
+      <c r="A742" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B742" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C742" t="s">
+        <v>8</v>
+      </c>
+      <c r="F742" s="14" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="743" spans="1:6">
+      <c r="A743" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B743" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C743" t="s">
+        <v>8</v>
+      </c>
+      <c r="F743" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="744" spans="1:6">
+      <c r="A744" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B744" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C744" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="745" spans="1:6">
+      <c r="A745" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B745" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D745">
+        <v>1200</v>
+      </c>
+      <c r="E745" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="746" spans="1:6">
+      <c r="A746" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B746" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D746">
+        <v>8000</v>
+      </c>
+      <c r="E746" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="747" spans="1:6">
+      <c r="A747" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B747" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C747" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="748" spans="1:6">
+      <c r="A748" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B748" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C748" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="749" spans="1:6">
+      <c r="A749" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="B749" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C749" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D749" s="10"/>
+      <c r="E749" s="10"/>
+      <c r="F749" s="21"/>
+    </row>
+    <row r="750" spans="1:6">
+      <c r="A750" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B750" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C750" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="751" spans="1:6">
+      <c r="A751" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B751" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F751" s="14" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="752" spans="1:6">
+      <c r="A752" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B752" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F752" s="14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="753" spans="1:6">
+      <c r="A753" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B753" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C753" t="s">
+        <v>8</v>
+      </c>
+      <c r="F753" s="14" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="754" spans="1:6">
+      <c r="A754" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B754" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C754" t="s">
+        <v>8</v>
+      </c>
+      <c r="F754" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="755" spans="1:6">
+      <c r="A755" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B755" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C755" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="756" spans="1:6">
+      <c r="A756" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B756" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C756" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="757" spans="1:6">
+      <c r="A757" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B757" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C757" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="758" spans="1:6">
+      <c r="A758" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B758" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C758" t="s">
+        <v>8</v>
+      </c>
+      <c r="F758" s="14" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="759" spans="1:6">
+      <c r="A759" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B759" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C759" t="s">
+        <v>8</v>
+      </c>
+      <c r="F759" s="14" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="760" spans="1:6">
+      <c r="A760" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B760" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C760" t="s">
+        <v>8</v>
+      </c>
+      <c r="F760" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="761" spans="1:6">
+      <c r="A761" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B761" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C761" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="762" spans="1:6">
+      <c r="A762" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B762" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D762">
+        <v>450</v>
+      </c>
+      <c r="E762" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="763" spans="1:6">
+      <c r="A763" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B763" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D763">
+        <v>-9999</v>
+      </c>
+      <c r="E763" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="764" spans="1:6">
+      <c r="A764" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B764" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C764" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="765" spans="1:6">
+      <c r="A765" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B765" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C765" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="766" spans="1:6">
+      <c r="A766" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="B766" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C766" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D766" s="10"/>
+      <c r="E766" s="10"/>
+      <c r="F766" s="21"/>
     </row>
   </sheetData>
+  <dataValidations count="10">
+    <dataValidation errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Data transfer " prompt="A list of all methods of data transfer from the device to a PC or a mobile phone such as Bluetooth version x, Wi-Fi,  (mini)SD-card, cable (e.g., hdmi, usb-c, or system specific). Methods are separated by ;" sqref="F345 F464 F447 F617 F736 F719 F260 F277 F294 F311 F328 F362 F379 F396 F413 F430 F481 F498" xr:uid="{DF380FD1-E52E-4890-B578-621A137B027B}"/>
+    <dataValidation errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Processed values" prompt="All the processed data which can be exported for analysis. Beware, the system may filterer and average over (large) time windows; check the computation details of the system before using these values." sqref="F258 F275 F292 F309 F326 F343 F360 F377 F394 F411 F462 F479 F496" xr:uid="{26935EF4-A791-48FC-8303-D0BFE747B87A}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Parameter sampling window" prompt="The window over which each parameter is calculated. The values indicate a range. For example, 1min:HR indicates heart rate is calculated for a window between 0 seconds to approx. 1 minute. 5 min: HR indicates it is calculated every 1 to approx. 5 mins" sqref="F259 F276 F293 F310 F327 F344 F361 F378 F395 F412 F429 F446 F463 F480 F497" xr:uid="{FBF721CF-AFFA-4BA9-95AF-DF18547814E6}"/>
+    <dataValidation errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Internal storage method" prompt="Availability and method of internal data storage with the following information structure: available (0/1); type (e.g., built-in storage, SD-card); comments" sqref="F267 F318 F352 F369 F386 F403 F420 F437 F454 F471 F488 F505" xr:uid="{9845DAD3-2A41-4E0C-94E0-BE2571B9B85D}"/>
+    <dataValidation errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Additional software" prompt="Additional software available (e.g., for analysis purposes) with the following information structure: Additional software available (0/1); list of all the additional software, separated by ; " sqref="F283 F317 F334 F351 F368 F402 F419 F453 F436" xr:uid="{CD10873C-FADE-4BD7-BB9E-05730CF661B8}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Required software" prompt="Software required to record and/or extract raw data with the following information structure: (0/1) (1 if required); list of all the software required to record, manage and export the data separated by ;" sqref="F316 F333 F350 F367 F384 F401 F418 F435 F452 F469 F486 F503" xr:uid="{EA14BB56-0EE2-4BEC-A9A6-49F7FA8AAC99}"/>
+    <dataValidation errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Server data storage " prompt="Data stored on external servers (including their location) with the following information structure: available (0/1); server location (country/countries/area, as specified by the manufacturer)." sqref="F319 F336 F353 F370 F404 F421 F438 F455 F472 F489" xr:uid="{CF51230E-163A-43AB-AA91-C3CE1D56C64F}"/>
+    <dataValidation errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="FDA approval" prompt="Device has been FDA approved/cleared (0/1); approval number if provided and specifications if approved for a specific feature or signal (e.g. Embrace Plus for epilepsy). " sqref="F323 F340 F357 F374 F408 F425 F442 F459" xr:uid="{F861F2FA-39AE-4979-9E78-7C3343A92040}"/>
+    <dataValidation errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Compatibility" prompt="System compatibility of the device (both mobile and computer) - all mobile operating systems supported, and their versions separated by ; followed by all the PC systems and their versions." sqref="F314 F331 F382:F383 F297:F298 F281 F399:F400 F416:F417 F433:F434 F450:F451 F467:F468" xr:uid="{520704B6-F05F-45AC-BCD1-C49D9E8DB105}"/>
+    <dataValidation errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Software required" prompt="software required to record and/or extract raw data with the following information structure: software required (0/1); list of all the software required to record, manage and export the data, separated by ;" sqref="F453 F436" xr:uid="{EE100393-7885-481B-8F3A-0FE4076E558D}"/>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006131D81E7FE36E44885B3A04523FCF5D" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3c9ab67dcfa560232a36bfe42a1cf3da">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="71842362-ab5d-46b4-b35f-08dc9c6328ce" xmlns:ns3="8def90a7-5747-4395-b698-a599996d7912" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="85c6a7f5c224f550ecad7291476c1ef0" ns2:_="" ns3:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71842362-ab5d-46b4-b35f-08dc9c6328ce">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="8def90a7-5747-4395-b698-a599996d7912" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006131D81E7FE36E44885B3A04523FCF5D" ma:contentTypeVersion="14" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="8f9efaeda295997044994eea58453835">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="71842362-ab5d-46b4-b35f-08dc9c6328ce" xmlns:ns3="8def90a7-5747-4395-b698-a599996d7912" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7a2e7ed8b28d563a97a27396956f6ac0" ns2:_="" ns3:_="">
     <xsd:import namespace="71842362-ab5d-46b4-b35f-08dc9c6328ce"/>
     <xsd:import namespace="8def90a7-5747-4395-b698-a599996d7912"/>
     <xsd:element name="properties">
@@ -4122,7 +11025,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="eaf58ba8-1e8d-4aec-a6f5-993f6032dc74" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Afbeeldingtags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="eaf58ba8-1e8d-4aec-a6f5-993f6032dc74" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -4176,7 +11079,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="20" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="20" nillable="true" ma:displayName="Gedeeld met" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -4195,7 +11098,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="21" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="21" nillable="true" ma:displayName="Gedeeld met details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -4212,8 +11115,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Inhoudstype"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titel"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -4302,34 +11205,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71842362-ab5d-46b4-b35f-08dc9c6328ce">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="8def90a7-5747-4395-b698-a599996d7912" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F528D5E-6FC3-4E0F-84AA-37A05AF01C85}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3C3AEBB-37B4-4BFB-8F88-26E487A619B6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3C3AEBB-37B4-4BFB-8F88-26E487A619B6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDBADEA2-FDC6-494D-BF37-E3AE079B5959}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="71842362-ab5d-46b4-b35f-08dc9c6328ce"/>
+    <ds:schemaRef ds:uri="8def90a7-5747-4395-b698-a599996d7912"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDBADEA2-FDC6-494D-BF37-E3AE079B5959}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8940976A-058B-4004-A4FC-ACB49E80C650}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="71842362-ab5d-46b4-b35f-08dc9c6328ce"/>
+    <ds:schemaRef ds:uri="8def90a7-5747-4395-b698-a599996d7912"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/raw/data_access.xlsx
+++ b/data/raw/data_access.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\msa583\Downloads\Relational Database_26-02-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zxu567\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4484C9E1-62F9-40C9-8CD2-6210A6186303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C05EC263-E747-450C-9A42-54BC239EC507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A7D6C86-A6AC-403C-91E2-C0E7310CD44B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2530" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2929" uniqueCount="345">
   <si>
     <t>device_id</t>
   </si>
@@ -931,6 +931,151 @@
   </si>
   <si>
     <t>Omnisense software</t>
+  </si>
+  <si>
+    <t>046_sia_wd_rin</t>
+  </si>
+  <si>
+    <t>Activity intensity, HR, HRV, RR, SpO2, Skin Temperature, Slepp Stages, Sleep Apnea Detection, Steps, Stress Index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1min: SpO2, 5min: HR, 1 hour: activity intensity, sleep stages, steps  </t>
+  </si>
+  <si>
+    <t>Bluetooth 5.0; Low power bluetooth module</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes </t>
+  </si>
+  <si>
+    <t>RingConn App</t>
+  </si>
+  <si>
+    <t>Apple Health, Google Fit or others to keep your data for longer</t>
+  </si>
+  <si>
+    <t>United Kingdom for users in the United States, the United Kingdom and the European Economic Area (EEA), and servers in People's Republic of China for users in People's Republic of China.</t>
+  </si>
+  <si>
+    <t>047_sia_wd_ult</t>
+  </si>
+  <si>
+    <t>HR;Sleep stages (with REM); Sleep efficiency score; Sleep restfulness score; Sleep time; HRV-RMSSD; HRV-SDNN; Stress score; Step Count; Distance; EE; VO2max; Atrial Fibrillation detection; Cardio Adaptability detection; Circadian Alignment Suggestions; RR; Blood oxygen saturation; Dynamic recovery score; Sleep movements; Movement score; Active minutes; Workout frequency; Detection of Stress periods; Detection of Relaxed periods; Detection of Stimulated periods; Detection of Active periods; Resting heart rate; Skin temp</t>
+  </si>
+  <si>
+    <t>5min: HRV; 30min: HR, Active minutes, Stress score; 1hour: Sleep movements; 1day: Sleep stages (with REM); Sleep efficiency score; Sleep restfulness score; Sleep time</t>
+  </si>
+  <si>
+    <t>Bluethooth low energy (BLE5)</t>
+  </si>
+  <si>
+    <t>Android 6 or later</t>
+  </si>
+  <si>
+    <t>iOS 15 or later</t>
+  </si>
+  <si>
+    <t>Ultrahuman App</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S., possibly india </t>
+  </si>
+  <si>
+    <t xml:space="preserve">it is mentioned that data can be collected, stored, and used in any country the company operates in, which is in India and therefore, not GDPR compliant </t>
+  </si>
+  <si>
+    <t>048_sia_wd_nua</t>
+  </si>
+  <si>
+    <t>DNE (Propriatory Nuanic index (1-100) derived from EDA and accelerometry)</t>
+  </si>
+  <si>
+    <t>1min: DNE</t>
+  </si>
+  <si>
+    <t>Bluetooth LE</t>
+  </si>
+  <si>
+    <t>Android 5 or higher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iOS 14 or higher </t>
+  </si>
+  <si>
+    <t>Nuanic App</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuanic Could will become available and will be GDPR compliant with data stored within the European Economic Area. Data might me processed outside of this area. Could storage will be optional and the integrated storage can still be used.  </t>
+  </si>
+  <si>
+    <t>data can be stored directly on the mobile device that runs the app</t>
+  </si>
+  <si>
+    <t>049_sia_wd_cos</t>
+  </si>
+  <si>
+    <t>Core Temperature; HR; RR; SpO2</t>
+  </si>
+  <si>
+    <t>c-med° App, and Cosinuss Health App0</t>
+  </si>
+  <si>
+    <t>Cosinuss Lab system</t>
+  </si>
+  <si>
+    <t>050_sia_wd_lum</t>
+  </si>
+  <si>
+    <t>Blood flow to the head; HR; HRV; Daily average flow index; Daily minimum flow index</t>
+  </si>
+  <si>
+    <t>5min: all</t>
+  </si>
+  <si>
+    <t>iOS 16 or later</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumia: Manage your dizziness app (available in US only) </t>
+  </si>
+  <si>
+    <t>051_sia_wd_plu</t>
+  </si>
+  <si>
+    <t>Breathing cycle amplitude parameters (max, mean, SD, root-mean-square and total energy estimation); breathing frequency parameters; RR; Breath-to-Breath Interval (BBI) parameters (min, max, mean, SD  root-mean-square and total BBI differences); 
+HRV parameters (SDNN, RMSSD, NN20, pNN20, pNN50); mean HR; NN50; ECG frequency parameters (VLF, LF, HF, peak frequency, absolute powers, normalized powers, LF/HF ratio);
+EMG activation-specific parameters (start, end, duration of muscle activation, latency, peak-to-peak amplitudes, root-mean-square, integral over activation segment);
+electrodermal response (EDR) latency; EDR amplitude, EDR rise time; EDR recovery time (to 50% and to 63% of EDR amplitude); Response peak after stimulus, total power estimation;
+maximum foce (N); force reproduction rate; jump height; fleight time during jump</t>
+  </si>
+  <si>
+    <t>Bluetooth 2.0+EDR, USB calbe to download stored data from memory (optional extra)</t>
+  </si>
+  <si>
+    <t>OepnSignals (r)evolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">default is 0 internal storage, but optionally available </t>
+  </si>
+  <si>
+    <t>052_sia_wd_plu</t>
+  </si>
+  <si>
+    <t>RR; breath-to-breath interval parameters (Minimum, maximum, mean, standard deviation &amp; root-mean-square of successive BBI differences); Breathing cycle amplitude parameters (Maximum, mean, standard deviation, root-mean-square &amp; total energy estimation); frequency parameters</t>
+  </si>
+  <si>
+    <t>Bluetooth required to transfer from device to phone; Flexible methods to transfer from phone application to computer.</t>
+  </si>
+  <si>
+    <t>for OpenSignals anlyses software</t>
+  </si>
+  <si>
+    <t>for Biosignals Studio Mobile Recording software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biosignals Studio </t>
+  </si>
+  <si>
+    <t>OpenSignals</t>
   </si>
 </sst>
 </file>
@@ -1075,7 +1220,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1130,6 +1275,9 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1465,7 +1613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA1BD5DC-A81B-4D9C-8626-3C643AFB0E7B}">
-  <dimension ref="A1:F766"/>
+  <dimension ref="A1:F886"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16.5546875" customWidth="1"/>
@@ -10938,6 +11086,1485 @@
       <c r="D766" s="10"/>
       <c r="E766" s="10"/>
       <c r="F766" s="21"/>
+    </row>
+    <row r="767" spans="1:6">
+      <c r="A767" t="s">
+        <v>0</v>
+      </c>
+      <c r="B767" t="s">
+        <v>1</v>
+      </c>
+      <c r="C767" t="s">
+        <v>2</v>
+      </c>
+      <c r="D767" t="s">
+        <v>3</v>
+      </c>
+      <c r="E767" t="s">
+        <v>4</v>
+      </c>
+      <c r="F767" s="14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="768" spans="1:6">
+      <c r="A768" t="s">
+        <v>298</v>
+      </c>
+      <c r="B768" t="s">
+        <v>7</v>
+      </c>
+      <c r="C768" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="769" spans="1:6">
+      <c r="A769" t="s">
+        <v>298</v>
+      </c>
+      <c r="B769" t="s">
+        <v>9</v>
+      </c>
+      <c r="F769" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="770" spans="1:6">
+      <c r="A770" t="s">
+        <v>298</v>
+      </c>
+      <c r="B770" t="s">
+        <v>11</v>
+      </c>
+      <c r="F770" s="14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="771" spans="1:6">
+      <c r="A771" t="s">
+        <v>298</v>
+      </c>
+      <c r="B771" t="s">
+        <v>12</v>
+      </c>
+      <c r="C771" t="s">
+        <v>8</v>
+      </c>
+      <c r="F771" s="14" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="772" spans="1:6">
+      <c r="A772" t="s">
+        <v>298</v>
+      </c>
+      <c r="B772" t="s">
+        <v>14</v>
+      </c>
+      <c r="C772" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="773" spans="1:6">
+      <c r="A773" t="s">
+        <v>298</v>
+      </c>
+      <c r="B773" t="s">
+        <v>16</v>
+      </c>
+      <c r="C773" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="774" spans="1:6">
+      <c r="A774" t="s">
+        <v>298</v>
+      </c>
+      <c r="B774" t="s">
+        <v>17</v>
+      </c>
+      <c r="C774" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="775" spans="1:6">
+      <c r="A775" t="s">
+        <v>298</v>
+      </c>
+      <c r="B775" t="s">
+        <v>19</v>
+      </c>
+      <c r="C775" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="776" spans="1:6">
+      <c r="A776" t="s">
+        <v>298</v>
+      </c>
+      <c r="B776" t="s">
+        <v>21</v>
+      </c>
+      <c r="C776" t="s">
+        <v>302</v>
+      </c>
+      <c r="F776" s="14" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="777" spans="1:6">
+      <c r="A777" t="s">
+        <v>298</v>
+      </c>
+      <c r="B777" t="s">
+        <v>23</v>
+      </c>
+      <c r="C777" t="s">
+        <v>8</v>
+      </c>
+      <c r="F777" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="778" spans="1:6">
+      <c r="A778" t="s">
+        <v>298</v>
+      </c>
+      <c r="B778" t="s">
+        <v>25</v>
+      </c>
+      <c r="C778" t="s">
+        <v>302</v>
+      </c>
+      <c r="F778" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="779" spans="1:6">
+      <c r="A779" t="s">
+        <v>298</v>
+      </c>
+      <c r="B779" t="s">
+        <v>27</v>
+      </c>
+      <c r="C779" t="s">
+        <v>8</v>
+      </c>
+      <c r="F779" s="14" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="780" spans="1:6">
+      <c r="A780" t="s">
+        <v>298</v>
+      </c>
+      <c r="B780" t="s">
+        <v>29</v>
+      </c>
+      <c r="D780">
+        <v>168</v>
+      </c>
+      <c r="E780" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="781" spans="1:6">
+      <c r="A781" t="s">
+        <v>298</v>
+      </c>
+      <c r="B781" t="s">
+        <v>31</v>
+      </c>
+      <c r="D781">
+        <v>-9999</v>
+      </c>
+      <c r="E781" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="782" spans="1:6">
+      <c r="A782" t="s">
+        <v>298</v>
+      </c>
+      <c r="B782" t="s">
+        <v>33</v>
+      </c>
+      <c r="C782" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="783" spans="1:6">
+      <c r="A783" t="s">
+        <v>298</v>
+      </c>
+      <c r="B783" t="s">
+        <v>34</v>
+      </c>
+      <c r="C783" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="784" spans="1:6">
+      <c r="A784" t="s">
+        <v>298</v>
+      </c>
+      <c r="B784" t="s">
+        <v>36</v>
+      </c>
+      <c r="C784" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="785" spans="1:6">
+      <c r="A785" t="s">
+        <v>306</v>
+      </c>
+      <c r="B785" t="s">
+        <v>7</v>
+      </c>
+      <c r="C785" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="786" spans="1:6">
+      <c r="A786" t="s">
+        <v>306</v>
+      </c>
+      <c r="B786" t="s">
+        <v>9</v>
+      </c>
+      <c r="F786" s="14" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="787" spans="1:6">
+      <c r="A787" t="s">
+        <v>306</v>
+      </c>
+      <c r="B787" t="s">
+        <v>11</v>
+      </c>
+      <c r="F787" s="14" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="788" spans="1:6">
+      <c r="A788" t="s">
+        <v>306</v>
+      </c>
+      <c r="B788" t="s">
+        <v>12</v>
+      </c>
+      <c r="C788" t="s">
+        <v>8</v>
+      </c>
+      <c r="F788" s="14" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="789" spans="1:6">
+      <c r="A789" t="s">
+        <v>306</v>
+      </c>
+      <c r="B789" t="s">
+        <v>14</v>
+      </c>
+      <c r="C789" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="790" spans="1:6">
+      <c r="A790" t="s">
+        <v>306</v>
+      </c>
+      <c r="B790" t="s">
+        <v>16</v>
+      </c>
+      <c r="C790" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="791" spans="1:6">
+      <c r="A791" t="s">
+        <v>306</v>
+      </c>
+      <c r="B791" t="s">
+        <v>17</v>
+      </c>
+      <c r="C791" t="s">
+        <v>8</v>
+      </c>
+      <c r="F791" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="792" spans="1:6">
+      <c r="A792" t="s">
+        <v>306</v>
+      </c>
+      <c r="B792" t="s">
+        <v>19</v>
+      </c>
+      <c r="C792" t="s">
+        <v>8</v>
+      </c>
+      <c r="F792" s="14" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="793" spans="1:6">
+      <c r="A793" t="s">
+        <v>306</v>
+      </c>
+      <c r="B793" t="s">
+        <v>21</v>
+      </c>
+      <c r="C793" t="s">
+        <v>8</v>
+      </c>
+      <c r="F793" s="14" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="794" spans="1:6">
+      <c r="A794" t="s">
+        <v>306</v>
+      </c>
+      <c r="B794" t="s">
+        <v>23</v>
+      </c>
+      <c r="C794" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="795" spans="1:6">
+      <c r="A795" t="s">
+        <v>306</v>
+      </c>
+      <c r="B795" t="s">
+        <v>25</v>
+      </c>
+      <c r="C795" t="s">
+        <v>8</v>
+      </c>
+      <c r="F795" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="796" spans="1:6">
+      <c r="A796" t="s">
+        <v>306</v>
+      </c>
+      <c r="B796" t="s">
+        <v>27</v>
+      </c>
+      <c r="C796" t="s">
+        <v>8</v>
+      </c>
+      <c r="F796" s="14" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="797" spans="1:6">
+      <c r="A797" t="s">
+        <v>306</v>
+      </c>
+      <c r="B797" t="s">
+        <v>29</v>
+      </c>
+      <c r="D797">
+        <v>168</v>
+      </c>
+      <c r="E797" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="798" spans="1:6">
+      <c r="A798" t="s">
+        <v>306</v>
+      </c>
+      <c r="B798" t="s">
+        <v>31</v>
+      </c>
+      <c r="D798">
+        <v>-9999</v>
+      </c>
+      <c r="E798" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="799" spans="1:6">
+      <c r="A799" t="s">
+        <v>306</v>
+      </c>
+      <c r="B799" t="s">
+        <v>33</v>
+      </c>
+      <c r="C799" t="s">
+        <v>35</v>
+      </c>
+      <c r="F799" s="14" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="800" spans="1:6">
+      <c r="A800" t="s">
+        <v>306</v>
+      </c>
+      <c r="B800" t="s">
+        <v>34</v>
+      </c>
+      <c r="C800" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="801" spans="1:6">
+      <c r="A801" t="s">
+        <v>306</v>
+      </c>
+      <c r="B801" t="s">
+        <v>36</v>
+      </c>
+      <c r="C801" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="802" spans="1:6">
+      <c r="A802" t="s">
+        <v>315</v>
+      </c>
+      <c r="B802" t="s">
+        <v>7</v>
+      </c>
+      <c r="C802" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="803" spans="1:6">
+      <c r="A803" t="s">
+        <v>315</v>
+      </c>
+      <c r="B803" t="s">
+        <v>9</v>
+      </c>
+      <c r="F803" s="14" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="804" spans="1:6">
+      <c r="A804" t="s">
+        <v>315</v>
+      </c>
+      <c r="B804" t="s">
+        <v>11</v>
+      </c>
+      <c r="F804" s="14" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="805" spans="1:6">
+      <c r="A805" t="s">
+        <v>315</v>
+      </c>
+      <c r="B805" t="s">
+        <v>12</v>
+      </c>
+      <c r="C805" t="s">
+        <v>8</v>
+      </c>
+      <c r="F805" s="14" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="806" spans="1:6">
+      <c r="A806" t="s">
+        <v>315</v>
+      </c>
+      <c r="B806" t="s">
+        <v>14</v>
+      </c>
+      <c r="C806" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="807" spans="1:6">
+      <c r="A807" t="s">
+        <v>315</v>
+      </c>
+      <c r="B807" t="s">
+        <v>16</v>
+      </c>
+      <c r="C807" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="808" spans="1:6">
+      <c r="A808" t="s">
+        <v>315</v>
+      </c>
+      <c r="B808" t="s">
+        <v>17</v>
+      </c>
+      <c r="C808" t="s">
+        <v>8</v>
+      </c>
+      <c r="F808" s="14" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="809" spans="1:6">
+      <c r="A809" t="s">
+        <v>315</v>
+      </c>
+      <c r="B809" t="s">
+        <v>19</v>
+      </c>
+      <c r="C809" t="s">
+        <v>8</v>
+      </c>
+      <c r="F809" s="14" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="810" spans="1:6">
+      <c r="A810" t="s">
+        <v>315</v>
+      </c>
+      <c r="B810" t="s">
+        <v>21</v>
+      </c>
+      <c r="C810" t="s">
+        <v>8</v>
+      </c>
+      <c r="F810" s="14" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="811" spans="1:6">
+      <c r="A811" t="s">
+        <v>315</v>
+      </c>
+      <c r="B811" t="s">
+        <v>23</v>
+      </c>
+      <c r="C811" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="812" spans="1:6">
+      <c r="A812" t="s">
+        <v>315</v>
+      </c>
+      <c r="B812" t="s">
+        <v>25</v>
+      </c>
+      <c r="C812" t="s">
+        <v>8</v>
+      </c>
+      <c r="F812" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="813" spans="1:6">
+      <c r="A813" t="s">
+        <v>315</v>
+      </c>
+      <c r="B813" t="s">
+        <v>27</v>
+      </c>
+      <c r="C813" t="s">
+        <v>35</v>
+      </c>
+      <c r="F813" s="14" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="814" spans="1:6">
+      <c r="A814" t="s">
+        <v>315</v>
+      </c>
+      <c r="B814" t="s">
+        <v>29</v>
+      </c>
+      <c r="D814">
+        <v>72</v>
+      </c>
+      <c r="E814" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="815" spans="1:6">
+      <c r="A815" t="s">
+        <v>315</v>
+      </c>
+      <c r="B815" t="s">
+        <v>31</v>
+      </c>
+      <c r="D815">
+        <v>-9999</v>
+      </c>
+      <c r="E815" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="816" spans="1:6">
+      <c r="A816" t="s">
+        <v>315</v>
+      </c>
+      <c r="B816" t="s">
+        <v>33</v>
+      </c>
+      <c r="C816" t="s">
+        <v>8</v>
+      </c>
+      <c r="F816" s="14" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="817" spans="1:6">
+      <c r="A817" t="s">
+        <v>315</v>
+      </c>
+      <c r="B817" t="s">
+        <v>34</v>
+      </c>
+      <c r="C817" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="818" spans="1:6">
+      <c r="A818" t="s">
+        <v>315</v>
+      </c>
+      <c r="B818" t="s">
+        <v>36</v>
+      </c>
+      <c r="C818" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="819" spans="1:6">
+      <c r="A819" t="s">
+        <v>324</v>
+      </c>
+      <c r="B819" t="s">
+        <v>7</v>
+      </c>
+      <c r="C819" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="820" spans="1:6">
+      <c r="A820" t="s">
+        <v>324</v>
+      </c>
+      <c r="B820" t="s">
+        <v>9</v>
+      </c>
+      <c r="F820" s="14" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="821" spans="1:6">
+      <c r="A821" t="s">
+        <v>324</v>
+      </c>
+      <c r="B821" t="s">
+        <v>11</v>
+      </c>
+      <c r="F821" s="14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="822" spans="1:6">
+      <c r="A822" t="s">
+        <v>324</v>
+      </c>
+      <c r="B822" t="s">
+        <v>12</v>
+      </c>
+      <c r="C822" t="s">
+        <v>8</v>
+      </c>
+      <c r="F822" s="14" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="823" spans="1:6">
+      <c r="A823" t="s">
+        <v>324</v>
+      </c>
+      <c r="B823" t="s">
+        <v>14</v>
+      </c>
+      <c r="C823" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="824" spans="1:6">
+      <c r="A824" t="s">
+        <v>324</v>
+      </c>
+      <c r="B824" t="s">
+        <v>16</v>
+      </c>
+      <c r="C824" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="825" spans="1:6">
+      <c r="A825" t="s">
+        <v>324</v>
+      </c>
+      <c r="B825" t="s">
+        <v>17</v>
+      </c>
+      <c r="C825" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="826" spans="1:6">
+      <c r="A826" t="s">
+        <v>324</v>
+      </c>
+      <c r="B826" t="s">
+        <v>19</v>
+      </c>
+      <c r="C826" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="827" spans="1:6">
+      <c r="A827" t="s">
+        <v>324</v>
+      </c>
+      <c r="B827" t="s">
+        <v>21</v>
+      </c>
+      <c r="C827" t="s">
+        <v>8</v>
+      </c>
+      <c r="F827" s="14" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="828" spans="1:6">
+      <c r="A828" t="s">
+        <v>324</v>
+      </c>
+      <c r="B828" t="s">
+        <v>23</v>
+      </c>
+      <c r="C828" t="s">
+        <v>8</v>
+      </c>
+      <c r="F828" s="14" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="829" spans="1:6">
+      <c r="A829" t="s">
+        <v>324</v>
+      </c>
+      <c r="B829" t="s">
+        <v>25</v>
+      </c>
+      <c r="C829" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="830" spans="1:6">
+      <c r="A830" t="s">
+        <v>324</v>
+      </c>
+      <c r="B830" t="s">
+        <v>27</v>
+      </c>
+      <c r="C830" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="831" spans="1:6">
+      <c r="A831" t="s">
+        <v>324</v>
+      </c>
+      <c r="B831" t="s">
+        <v>29</v>
+      </c>
+      <c r="D831">
+        <v>-9999</v>
+      </c>
+      <c r="E831" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="832" spans="1:6">
+      <c r="A832" t="s">
+        <v>324</v>
+      </c>
+      <c r="B832" t="s">
+        <v>31</v>
+      </c>
+      <c r="D832">
+        <v>-9999</v>
+      </c>
+      <c r="E832" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="833" spans="1:6">
+      <c r="A833" t="s">
+        <v>324</v>
+      </c>
+      <c r="B833" t="s">
+        <v>33</v>
+      </c>
+      <c r="C833" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="834" spans="1:6">
+      <c r="A834" t="s">
+        <v>324</v>
+      </c>
+      <c r="B834" t="s">
+        <v>34</v>
+      </c>
+      <c r="C834" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="835" spans="1:6">
+      <c r="A835" t="s">
+        <v>324</v>
+      </c>
+      <c r="B835" t="s">
+        <v>36</v>
+      </c>
+      <c r="C835" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="836" spans="1:6">
+      <c r="A836" t="s">
+        <v>328</v>
+      </c>
+      <c r="B836" t="s">
+        <v>7</v>
+      </c>
+      <c r="C836" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="837" spans="1:6">
+      <c r="A837" t="s">
+        <v>328</v>
+      </c>
+      <c r="B837" t="s">
+        <v>9</v>
+      </c>
+      <c r="F837" s="14" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="838" spans="1:6">
+      <c r="A838" t="s">
+        <v>328</v>
+      </c>
+      <c r="B838" t="s">
+        <v>11</v>
+      </c>
+      <c r="F838" s="14" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="839" spans="1:6">
+      <c r="A839" t="s">
+        <v>328</v>
+      </c>
+      <c r="B839" t="s">
+        <v>12</v>
+      </c>
+      <c r="F839" s="14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="840" spans="1:6">
+      <c r="A840" t="s">
+        <v>328</v>
+      </c>
+      <c r="B840" t="s">
+        <v>14</v>
+      </c>
+      <c r="C840" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="841" spans="1:6">
+      <c r="A841" t="s">
+        <v>328</v>
+      </c>
+      <c r="B841" t="s">
+        <v>16</v>
+      </c>
+      <c r="C841" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="842" spans="1:6">
+      <c r="A842" t="s">
+        <v>328</v>
+      </c>
+      <c r="B842" t="s">
+        <v>17</v>
+      </c>
+      <c r="C842" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="843" spans="1:6">
+      <c r="A843" t="s">
+        <v>328</v>
+      </c>
+      <c r="B843" t="s">
+        <v>19</v>
+      </c>
+      <c r="C843" t="s">
+        <v>8</v>
+      </c>
+      <c r="F843" s="14" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="844" spans="1:6">
+      <c r="A844" t="s">
+        <v>328</v>
+      </c>
+      <c r="B844" t="s">
+        <v>21</v>
+      </c>
+      <c r="C844" t="s">
+        <v>8</v>
+      </c>
+      <c r="F844" s="14" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="845" spans="1:6">
+      <c r="A845" t="s">
+        <v>328</v>
+      </c>
+      <c r="B845" t="s">
+        <v>23</v>
+      </c>
+      <c r="C845" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="846" spans="1:6">
+      <c r="A846" t="s">
+        <v>328</v>
+      </c>
+      <c r="B846" t="s">
+        <v>25</v>
+      </c>
+      <c r="C846" t="s">
+        <v>8</v>
+      </c>
+      <c r="F846" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="847" spans="1:6">
+      <c r="A847" t="s">
+        <v>328</v>
+      </c>
+      <c r="B847" t="s">
+        <v>27</v>
+      </c>
+      <c r="C847" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="848" spans="1:6">
+      <c r="A848" t="s">
+        <v>328</v>
+      </c>
+      <c r="B848" t="s">
+        <v>29</v>
+      </c>
+      <c r="D848">
+        <v>-9999</v>
+      </c>
+      <c r="E848" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="849" spans="1:6">
+      <c r="A849" t="s">
+        <v>328</v>
+      </c>
+      <c r="B849" t="s">
+        <v>31</v>
+      </c>
+      <c r="D849">
+        <v>-9999</v>
+      </c>
+      <c r="E849" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="850" spans="1:6">
+      <c r="A850" t="s">
+        <v>328</v>
+      </c>
+      <c r="B850" t="s">
+        <v>33</v>
+      </c>
+      <c r="C850" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="851" spans="1:6">
+      <c r="A851" t="s">
+        <v>328</v>
+      </c>
+      <c r="B851" t="s">
+        <v>34</v>
+      </c>
+      <c r="C851" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="852" spans="1:6">
+      <c r="A852" t="s">
+        <v>328</v>
+      </c>
+      <c r="B852" t="s">
+        <v>36</v>
+      </c>
+      <c r="C852" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="853" spans="1:6">
+      <c r="A853" t="s">
+        <v>333</v>
+      </c>
+      <c r="B853" t="s">
+        <v>7</v>
+      </c>
+      <c r="C853" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="854" spans="1:6">
+      <c r="A854" t="s">
+        <v>333</v>
+      </c>
+      <c r="B854" t="s">
+        <v>9</v>
+      </c>
+      <c r="F854" s="30" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="855" spans="1:6">
+      <c r="A855" t="s">
+        <v>333</v>
+      </c>
+      <c r="B855" t="s">
+        <v>11</v>
+      </c>
+      <c r="F855" s="14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="856" spans="1:6">
+      <c r="A856" t="s">
+        <v>333</v>
+      </c>
+      <c r="B856" t="s">
+        <v>12</v>
+      </c>
+      <c r="C856" t="s">
+        <v>8</v>
+      </c>
+      <c r="F856" s="14" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="857" spans="1:6">
+      <c r="A857" t="s">
+        <v>333</v>
+      </c>
+      <c r="B857" t="s">
+        <v>14</v>
+      </c>
+      <c r="C857" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="858" spans="1:6">
+      <c r="A858" t="s">
+        <v>333</v>
+      </c>
+      <c r="B858" t="s">
+        <v>16</v>
+      </c>
+      <c r="C858" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="859" spans="1:6">
+      <c r="A859" t="s">
+        <v>333</v>
+      </c>
+      <c r="B859" t="s">
+        <v>17</v>
+      </c>
+      <c r="C859" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="860" spans="1:6">
+      <c r="A860" t="s">
+        <v>333</v>
+      </c>
+      <c r="B860" t="s">
+        <v>19</v>
+      </c>
+      <c r="C860" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="861" spans="1:6">
+      <c r="A861" t="s">
+        <v>333</v>
+      </c>
+      <c r="B861" t="s">
+        <v>21</v>
+      </c>
+      <c r="C861" t="s">
+        <v>8</v>
+      </c>
+      <c r="F861" s="14" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="862" spans="1:6">
+      <c r="A862" t="s">
+        <v>333</v>
+      </c>
+      <c r="B862" t="s">
+        <v>23</v>
+      </c>
+      <c r="C862" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="863" spans="1:6">
+      <c r="A863" t="s">
+        <v>333</v>
+      </c>
+      <c r="B863" t="s">
+        <v>25</v>
+      </c>
+      <c r="C863" t="s">
+        <v>8</v>
+      </c>
+      <c r="F863" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="864" spans="1:6">
+      <c r="A864" t="s">
+        <v>333</v>
+      </c>
+      <c r="B864" t="s">
+        <v>27</v>
+      </c>
+      <c r="C864" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="865" spans="1:6">
+      <c r="A865" t="s">
+        <v>333</v>
+      </c>
+      <c r="B865" t="s">
+        <v>29</v>
+      </c>
+      <c r="D865">
+        <v>111</v>
+      </c>
+      <c r="E865" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="866" spans="1:6">
+      <c r="A866" t="s">
+        <v>333</v>
+      </c>
+      <c r="B866" t="s">
+        <v>31</v>
+      </c>
+      <c r="D866">
+        <v>8000</v>
+      </c>
+      <c r="E866" t="s">
+        <v>32</v>
+      </c>
+      <c r="F866" s="14" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="867" spans="1:6">
+      <c r="A867" t="s">
+        <v>333</v>
+      </c>
+      <c r="B867" t="s">
+        <v>33</v>
+      </c>
+      <c r="C867" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="868" spans="1:6">
+      <c r="A868" t="s">
+        <v>333</v>
+      </c>
+      <c r="B868" t="s">
+        <v>34</v>
+      </c>
+      <c r="C868" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="869" spans="1:6">
+      <c r="A869" t="s">
+        <v>333</v>
+      </c>
+      <c r="B869" t="s">
+        <v>36</v>
+      </c>
+      <c r="C869" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="870" spans="1:6">
+      <c r="A870" t="s">
+        <v>338</v>
+      </c>
+      <c r="B870" t="s">
+        <v>7</v>
+      </c>
+      <c r="C870" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="871" spans="1:6">
+      <c r="A871" t="s">
+        <v>338</v>
+      </c>
+      <c r="B871" t="s">
+        <v>9</v>
+      </c>
+      <c r="F871" s="14" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="872" spans="1:6">
+      <c r="A872" t="s">
+        <v>338</v>
+      </c>
+      <c r="B872" t="s">
+        <v>11</v>
+      </c>
+      <c r="F872" s="14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="873" spans="1:6">
+      <c r="A873" t="s">
+        <v>338</v>
+      </c>
+      <c r="B873" t="s">
+        <v>12</v>
+      </c>
+      <c r="C873" t="s">
+        <v>8</v>
+      </c>
+      <c r="F873" s="14" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="874" spans="1:6">
+      <c r="A874" t="s">
+        <v>338</v>
+      </c>
+      <c r="B874" t="s">
+        <v>14</v>
+      </c>
+      <c r="C874" t="s">
+        <v>8</v>
+      </c>
+      <c r="F874" s="14" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="875" spans="1:6">
+      <c r="A875" t="s">
+        <v>338</v>
+      </c>
+      <c r="B875" t="s">
+        <v>16</v>
+      </c>
+      <c r="C875" t="s">
+        <v>8</v>
+      </c>
+      <c r="F875" s="14" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="876" spans="1:6">
+      <c r="A876" t="s">
+        <v>338</v>
+      </c>
+      <c r="B876" t="s">
+        <v>17</v>
+      </c>
+      <c r="C876" t="s">
+        <v>8</v>
+      </c>
+      <c r="F876" s="14" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="877" spans="1:6">
+      <c r="A877" t="s">
+        <v>338</v>
+      </c>
+      <c r="B877" t="s">
+        <v>19</v>
+      </c>
+      <c r="C877" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="878" spans="1:6">
+      <c r="A878" t="s">
+        <v>338</v>
+      </c>
+      <c r="B878" t="s">
+        <v>21</v>
+      </c>
+      <c r="C878" t="s">
+        <v>8</v>
+      </c>
+      <c r="F878" s="14" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="879" spans="1:6">
+      <c r="A879" t="s">
+        <v>338</v>
+      </c>
+      <c r="B879" t="s">
+        <v>23</v>
+      </c>
+      <c r="C879" t="s">
+        <v>8</v>
+      </c>
+      <c r="F879" s="14" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="880" spans="1:6">
+      <c r="A880" t="s">
+        <v>338</v>
+      </c>
+      <c r="B880" t="s">
+        <v>25</v>
+      </c>
+      <c r="C880" t="s">
+        <v>8</v>
+      </c>
+      <c r="F880" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="881" spans="1:5">
+      <c r="A881" t="s">
+        <v>338</v>
+      </c>
+      <c r="B881" t="s">
+        <v>27</v>
+      </c>
+      <c r="C881" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="882" spans="1:5">
+      <c r="A882" t="s">
+        <v>338</v>
+      </c>
+      <c r="B882" t="s">
+        <v>29</v>
+      </c>
+      <c r="D882">
+        <v>10</v>
+      </c>
+      <c r="E882" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="883" spans="1:5">
+      <c r="A883" t="s">
+        <v>338</v>
+      </c>
+      <c r="B883" t="s">
+        <v>31</v>
+      </c>
+      <c r="D883">
+        <v>-9999</v>
+      </c>
+      <c r="E883" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="884" spans="1:5">
+      <c r="A884" t="s">
+        <v>338</v>
+      </c>
+      <c r="B884" t="s">
+        <v>33</v>
+      </c>
+      <c r="C884" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="885" spans="1:5">
+      <c r="A885" t="s">
+        <v>338</v>
+      </c>
+      <c r="B885" t="s">
+        <v>34</v>
+      </c>
+      <c r="C885" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="886" spans="1:5">
+      <c r="A886" t="s">
+        <v>338</v>
+      </c>
+      <c r="B886" t="s">
+        <v>36</v>
+      </c>
+      <c r="C886" t="s">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="10">
@@ -10966,17 +12593,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71842362-ab5d-46b4-b35f-08dc9c6328ce">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="8def90a7-5747-4395-b698-a599996d7912" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006131D81E7FE36E44885B3A04523FCF5D" ma:contentTypeVersion="14" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="8f9efaeda295997044994eea58453835">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="71842362-ab5d-46b4-b35f-08dc9c6328ce" xmlns:ns3="8def90a7-5747-4395-b698-a599996d7912" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7a2e7ed8b28d563a97a27396956f6ac0" ns2:_="" ns3:_="">
     <xsd:import namespace="71842362-ab5d-46b4-b35f-08dc9c6328ce"/>
@@ -11205,6 +12821,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71842362-ab5d-46b4-b35f-08dc9c6328ce">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="8def90a7-5747-4395-b698-a599996d7912" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3C3AEBB-37B4-4BFB-8F88-26E487A619B6}">
   <ds:schemaRefs>
@@ -11214,17 +12841,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDBADEA2-FDC6-494D-BF37-E3AE079B5959}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="71842362-ab5d-46b4-b35f-08dc9c6328ce"/>
-    <ds:schemaRef ds:uri="8def90a7-5747-4395-b698-a599996d7912"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8940976A-058B-4004-A4FC-ACB49E80C650}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11241,4 +12857,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDBADEA2-FDC6-494D-BF37-E3AE079B5959}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="71842362-ab5d-46b4-b35f-08dc9c6328ce"/>
+    <ds:schemaRef ds:uri="8def90a7-5747-4395-b698-a599996d7912"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>